--- a/datosIntentosOutput.xlsx
+++ b/datosIntentosOutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S675"/>
+  <dimension ref="A1:U675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -578,6 +588,16 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -637,6 +657,16 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -696,6 +726,12 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
+      <c r="T4" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -755,6 +791,12 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="n">
+        <v>80</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -812,6 +854,12 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -873,6 +921,12 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
+      <c r="T7" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -932,6 +986,12 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
+      <c r="T8" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U8" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -991,6 +1051,12 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
+      <c r="T9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1050,6 +1116,12 @@
       <c r="S10" t="n">
         <v>1</v>
       </c>
+      <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1109,6 +1181,12 @@
       <c r="S11" t="n">
         <v>1</v>
       </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1168,6 +1246,16 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1227,6 +1315,12 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="n">
+        <v>75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1286,6 +1380,12 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1345,6 +1445,16 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1404,6 +1514,16 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1463,6 +1583,16 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1522,6 +1652,16 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1581,6 +1721,12 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
+      <c r="T19" t="n">
+        <v>50</v>
+      </c>
+      <c r="U19" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1640,6 +1786,12 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
+      <c r="T20" t="n">
+        <v>75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1699,6 +1851,12 @@
       <c r="S21" t="n">
         <v>0</v>
       </c>
+      <c r="T21" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1758,6 +1916,12 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U22" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1817,6 +1981,12 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
+      <c r="T23" t="n">
+        <v>100</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1876,6 +2046,12 @@
       <c r="S24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="n">
+        <v>100</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1935,6 +2111,12 @@
       <c r="S25" t="n">
         <v>0</v>
       </c>
+      <c r="T25" t="n">
+        <v>50</v>
+      </c>
+      <c r="U25" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1994,6 +2176,12 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
+      <c r="T26" t="n">
+        <v>100</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2053,6 +2241,12 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
+      <c r="T27" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U27" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2112,6 +2306,12 @@
       <c r="S28" t="n">
         <v>0</v>
       </c>
+      <c r="T28" t="n">
+        <v>50</v>
+      </c>
+      <c r="U28" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2171,6 +2371,12 @@
       <c r="S29" t="n">
         <v>0</v>
       </c>
+      <c r="T29" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2230,6 +2436,12 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2289,6 +2501,12 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
+      <c r="T31" t="n">
+        <v>50</v>
+      </c>
+      <c r="U31" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2348,6 +2566,12 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
+      <c r="T32" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2407,6 +2631,16 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2466,6 +2700,16 @@
       <c r="S34" t="n">
         <v>0</v>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2525,6 +2769,12 @@
       <c r="S35" t="n">
         <v>0</v>
       </c>
+      <c r="T35" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2584,6 +2834,12 @@
       <c r="S36" t="n">
         <v>0</v>
       </c>
+      <c r="T36" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2643,6 +2899,12 @@
       <c r="S37" t="n">
         <v>0</v>
       </c>
+      <c r="T37" t="n">
+        <v>100</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2702,6 +2964,16 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2761,6 +3033,16 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2820,6 +3102,12 @@
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="n">
+        <v>50</v>
+      </c>
+      <c r="U40" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2879,6 +3167,12 @@
       <c r="S41" t="n">
         <v>0</v>
       </c>
+      <c r="T41" t="n">
+        <v>100</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2938,6 +3232,12 @@
       <c r="S42" t="n">
         <v>0</v>
       </c>
+      <c r="T42" t="n">
+        <v>100</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2997,6 +3297,12 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
+      <c r="T43" t="n">
+        <v>100</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3056,6 +3362,12 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
+      <c r="T44" t="n">
+        <v>100</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3115,6 +3427,12 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="T45" t="n">
+        <v>100</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3174,6 +3492,12 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
+      <c r="T46" t="n">
+        <v>100</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3233,6 +3557,12 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
+      <c r="T47" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U47" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3292,6 +3622,12 @@
       <c r="S48" t="n">
         <v>0</v>
       </c>
+      <c r="T48" t="n">
+        <v>100</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3351,6 +3687,16 @@
       <c r="S49" t="n">
         <v>0</v>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3410,6 +3756,16 @@
       <c r="S50" t="n">
         <v>0</v>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3469,6 +3825,16 @@
       <c r="S51" t="n">
         <v>0</v>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3528,6 +3894,16 @@
       <c r="S52" t="n">
         <v>2</v>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3587,6 +3963,16 @@
       <c r="S53" t="n">
         <v>0</v>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3646,6 +4032,16 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3705,6 +4101,16 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3764,6 +4170,12 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
+      <c r="T56" t="n">
+        <v>100</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3823,6 +4235,12 @@
       <c r="S57" t="n">
         <v>0</v>
       </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3882,6 +4300,12 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -3941,6 +4365,12 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
+      <c r="T59" t="n">
+        <v>100</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4000,6 +4430,12 @@
       <c r="S60" t="n">
         <v>1</v>
       </c>
+      <c r="T60" t="n">
+        <v>50</v>
+      </c>
+      <c r="U60" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4059,6 +4495,12 @@
       <c r="S61" t="n">
         <v>0</v>
       </c>
+      <c r="T61" t="n">
+        <v>100</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4118,6 +4560,12 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
+      <c r="T62" t="n">
+        <v>100</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4177,6 +4625,12 @@
       <c r="S63" t="n">
         <v>1</v>
       </c>
+      <c r="T63" t="n">
+        <v>100</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4236,6 +4690,12 @@
       <c r="S64" t="n">
         <v>0</v>
       </c>
+      <c r="T64" t="n">
+        <v>100</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4295,6 +4755,12 @@
       <c r="S65" t="n">
         <v>0</v>
       </c>
+      <c r="T65" t="n">
+        <v>100</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4354,6 +4820,12 @@
       <c r="S66" t="n">
         <v>0</v>
       </c>
+      <c r="T66" t="n">
+        <v>100</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4413,6 +4885,12 @@
       <c r="S67" t="n">
         <v>1</v>
       </c>
+      <c r="T67" t="n">
+        <v>100</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4472,6 +4950,12 @@
       <c r="S68" t="n">
         <v>2</v>
       </c>
+      <c r="T68" t="n">
+        <v>100</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4531,6 +5015,12 @@
       <c r="S69" t="n">
         <v>0</v>
       </c>
+      <c r="T69" t="n">
+        <v>75</v>
+      </c>
+      <c r="U69" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4590,6 +5080,16 @@
       <c r="S70" t="n">
         <v>0</v>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4649,6 +5149,16 @@
       <c r="S71" t="n">
         <v>0</v>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4708,6 +5218,16 @@
       <c r="S72" t="n">
         <v>0</v>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4767,6 +5287,12 @@
       <c r="S73" t="n">
         <v>0</v>
       </c>
+      <c r="T73" t="n">
+        <v>100</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4826,6 +5352,12 @@
       <c r="S74" t="n">
         <v>0</v>
       </c>
+      <c r="T74" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U74" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4885,6 +5417,12 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
+      <c r="T75" t="n">
+        <v>100</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4944,6 +5482,12 @@
       <c r="S76" t="n">
         <v>0</v>
       </c>
+      <c r="T76" t="n">
+        <v>100</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5003,6 +5547,12 @@
       <c r="S77" t="n">
         <v>0</v>
       </c>
+      <c r="T77" t="n">
+        <v>100</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5062,6 +5612,16 @@
       <c r="S78" t="n">
         <v>0</v>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -5121,6 +5681,12 @@
       <c r="S79" t="n">
         <v>0</v>
       </c>
+      <c r="T79" t="n">
+        <v>100</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -5180,6 +5746,12 @@
       <c r="S80" t="n">
         <v>0</v>
       </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -5239,6 +5811,12 @@
       <c r="S81" t="n">
         <v>0</v>
       </c>
+      <c r="T81" t="n">
+        <v>100</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5298,6 +5876,12 @@
       <c r="S82" t="n">
         <v>0</v>
       </c>
+      <c r="T82" t="n">
+        <v>100</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5357,6 +5941,12 @@
       <c r="S83" t="n">
         <v>0</v>
       </c>
+      <c r="T83" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U83" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5416,6 +6006,12 @@
       <c r="S84" t="n">
         <v>0</v>
       </c>
+      <c r="T84" t="n">
+        <v>100</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5475,6 +6071,12 @@
       <c r="S85" t="n">
         <v>0</v>
       </c>
+      <c r="T85" t="n">
+        <v>100</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5534,6 +6136,16 @@
       <c r="S86" t="n">
         <v>0</v>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5593,6 +6205,12 @@
       <c r="S87" t="n">
         <v>0</v>
       </c>
+      <c r="T87" t="n">
+        <v>100</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5652,6 +6270,12 @@
       <c r="S88" t="n">
         <v>0</v>
       </c>
+      <c r="T88" t="n">
+        <v>100</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -5711,6 +6335,16 @@
       <c r="S89" t="n">
         <v>1</v>
       </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -5770,6 +6404,16 @@
       <c r="S90" t="n">
         <v>0</v>
       </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -5829,6 +6473,12 @@
       <c r="S91" t="n">
         <v>0</v>
       </c>
+      <c r="T91" t="n">
+        <v>100</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -5888,6 +6538,12 @@
       <c r="S92" t="n">
         <v>0</v>
       </c>
+      <c r="T92" t="n">
+        <v>25</v>
+      </c>
+      <c r="U92" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -5947,6 +6603,12 @@
       <c r="S93" t="n">
         <v>0</v>
       </c>
+      <c r="T93" t="n">
+        <v>50</v>
+      </c>
+      <c r="U93" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -6006,6 +6668,12 @@
       <c r="S94" t="n">
         <v>0</v>
       </c>
+      <c r="T94" t="n">
+        <v>100</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -6065,6 +6733,12 @@
       <c r="S95" t="n">
         <v>0</v>
       </c>
+      <c r="T95" t="n">
+        <v>100</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -6124,6 +6798,12 @@
       <c r="S96" t="n">
         <v>0</v>
       </c>
+      <c r="T96" t="n">
+        <v>100</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -6183,6 +6863,12 @@
       <c r="S97" t="n">
         <v>0</v>
       </c>
+      <c r="T97" t="n">
+        <v>100</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -6242,6 +6928,12 @@
       <c r="S98" t="n">
         <v>0</v>
       </c>
+      <c r="T98" t="n">
+        <v>100</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -6301,6 +6993,12 @@
       <c r="S99" t="n">
         <v>0</v>
       </c>
+      <c r="T99" t="n">
+        <v>50</v>
+      </c>
+      <c r="U99" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -6360,6 +7058,12 @@
       <c r="S100" t="n">
         <v>0</v>
       </c>
+      <c r="T100" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U100" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6419,6 +7123,16 @@
       <c r="S101" t="n">
         <v>0</v>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6477,6 +7191,16 @@
       </c>
       <c r="S102" t="n">
         <v>0</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6537,6 +7261,12 @@
       <c r="S103" t="n">
         <v>0</v>
       </c>
+      <c r="T103" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U103" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6596,6 +7326,12 @@
       <c r="S104" t="n">
         <v>0</v>
       </c>
+      <c r="T104" t="n">
+        <v>100</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -6655,6 +7391,12 @@
       <c r="S105" t="n">
         <v>1</v>
       </c>
+      <c r="T105" t="n">
+        <v>50</v>
+      </c>
+      <c r="U105" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -6714,6 +7456,12 @@
       <c r="S106" t="n">
         <v>0</v>
       </c>
+      <c r="T106" t="n">
+        <v>100</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -6773,6 +7521,12 @@
       <c r="S107" t="n">
         <v>0</v>
       </c>
+      <c r="T107" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U107" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -6832,6 +7586,12 @@
       <c r="S108" t="n">
         <v>0</v>
       </c>
+      <c r="T108" t="n">
+        <v>100</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -6891,6 +7651,12 @@
       <c r="S109" t="n">
         <v>0</v>
       </c>
+      <c r="T109" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U109" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -6950,6 +7716,16 @@
       <c r="S110" t="n">
         <v>0</v>
       </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -7009,6 +7785,16 @@
       <c r="S111" t="n">
         <v>0</v>
       </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -7068,6 +7854,12 @@
       <c r="S112" t="n">
         <v>0</v>
       </c>
+      <c r="T112" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="U112" t="n">
+        <v>43.75</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -7127,6 +7919,12 @@
       <c r="S113" t="n">
         <v>0</v>
       </c>
+      <c r="T113" t="n">
+        <v>100</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -7186,6 +7984,12 @@
       <c r="S114" t="n">
         <v>0</v>
       </c>
+      <c r="T114" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U114" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -7245,6 +8049,12 @@
       <c r="S115" t="n">
         <v>0</v>
       </c>
+      <c r="T115" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U115" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -7304,6 +8114,12 @@
       <c r="S116" t="n">
         <v>0</v>
       </c>
+      <c r="T116" t="n">
+        <v>100</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7363,6 +8179,12 @@
       <c r="S117" t="n">
         <v>0</v>
       </c>
+      <c r="T117" t="n">
+        <v>100</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7422,6 +8244,12 @@
       <c r="S118" t="n">
         <v>0</v>
       </c>
+      <c r="T118" t="n">
+        <v>100</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7481,6 +8309,12 @@
       <c r="S119" t="n">
         <v>0</v>
       </c>
+      <c r="T119" t="n">
+        <v>100</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7540,6 +8374,16 @@
       <c r="S120" t="n">
         <v>0</v>
       </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -7599,6 +8443,12 @@
       <c r="S121" t="n">
         <v>0</v>
       </c>
+      <c r="T121" t="n">
+        <v>100</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -7658,6 +8508,12 @@
       <c r="S122" t="n">
         <v>0</v>
       </c>
+      <c r="T122" t="n">
+        <v>60</v>
+      </c>
+      <c r="U122" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -7717,6 +8573,12 @@
       <c r="S123" t="n">
         <v>0</v>
       </c>
+      <c r="T123" t="n">
+        <v>100</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -7776,6 +8638,16 @@
       <c r="S124" t="n">
         <v>0</v>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -7835,6 +8707,16 @@
       <c r="S125" t="n">
         <v>0</v>
       </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -7894,6 +8776,16 @@
       <c r="S126" t="n">
         <v>0</v>
       </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -7953,6 +8845,12 @@
       <c r="S127" t="n">
         <v>0</v>
       </c>
+      <c r="T127" t="n">
+        <v>100</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -8012,6 +8910,12 @@
       <c r="S128" t="n">
         <v>0</v>
       </c>
+      <c r="T128" t="n">
+        <v>100</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -8071,6 +8975,12 @@
       <c r="S129" t="n">
         <v>0</v>
       </c>
+      <c r="T129" t="n">
+        <v>100</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -8130,6 +9040,12 @@
       <c r="S130" t="n">
         <v>0</v>
       </c>
+      <c r="T130" t="n">
+        <v>75</v>
+      </c>
+      <c r="U130" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -8189,6 +9105,12 @@
       <c r="S131" t="n">
         <v>0</v>
       </c>
+      <c r="T131" t="n">
+        <v>100</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -8248,6 +9170,12 @@
       <c r="S132" t="n">
         <v>0</v>
       </c>
+      <c r="T132" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U132" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -8307,6 +9235,12 @@
       <c r="S133" t="n">
         <v>0</v>
       </c>
+      <c r="T133" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U133" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -8366,6 +9300,12 @@
       <c r="S134" t="n">
         <v>0</v>
       </c>
+      <c r="T134" t="n">
+        <v>100</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -8425,6 +9365,12 @@
       <c r="S135" t="n">
         <v>0</v>
       </c>
+      <c r="T135" t="n">
+        <v>100</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -8484,6 +9430,12 @@
       <c r="S136" t="n">
         <v>0</v>
       </c>
+      <c r="T136" t="n">
+        <v>100</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -8543,6 +9495,12 @@
       <c r="S137" t="n">
         <v>0</v>
       </c>
+      <c r="T137" t="n">
+        <v>100</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -8602,6 +9560,12 @@
       <c r="S138" t="n">
         <v>1</v>
       </c>
+      <c r="T138" t="n">
+        <v>80</v>
+      </c>
+      <c r="U138" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -8661,6 +9625,12 @@
       <c r="S139" t="n">
         <v>0</v>
       </c>
+      <c r="T139" t="n">
+        <v>80</v>
+      </c>
+      <c r="U139" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -8720,6 +9690,12 @@
       <c r="S140" t="n">
         <v>0</v>
       </c>
+      <c r="T140" t="n">
+        <v>100</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -8779,6 +9755,12 @@
       <c r="S141" t="n">
         <v>0</v>
       </c>
+      <c r="T141" t="n">
+        <v>100</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -8838,6 +9820,12 @@
       <c r="S142" t="n">
         <v>0</v>
       </c>
+      <c r="T142" t="n">
+        <v>100</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -8897,6 +9885,16 @@
       <c r="S143" t="n">
         <v>0</v>
       </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -8956,6 +9954,12 @@
       <c r="S144" t="n">
         <v>0</v>
       </c>
+      <c r="T144" t="n">
+        <v>75</v>
+      </c>
+      <c r="U144" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -9015,6 +10019,12 @@
       <c r="S145" t="n">
         <v>0</v>
       </c>
+      <c r="T145" t="n">
+        <v>100</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -9074,6 +10084,16 @@
       <c r="S146" t="n">
         <v>0</v>
       </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -9133,6 +10153,12 @@
       <c r="S147" t="n">
         <v>0</v>
       </c>
+      <c r="T147" t="n">
+        <v>80</v>
+      </c>
+      <c r="U147" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -9192,6 +10218,16 @@
       <c r="S148" t="n">
         <v>0</v>
       </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -9251,6 +10287,16 @@
       <c r="S149" t="n">
         <v>0</v>
       </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -9310,6 +10356,12 @@
       <c r="S150" t="n">
         <v>0</v>
       </c>
+      <c r="T150" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U150" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -9369,6 +10421,12 @@
       <c r="S151" t="n">
         <v>0</v>
       </c>
+      <c r="T151" t="n">
+        <v>100</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -9428,6 +10486,16 @@
       <c r="S152" t="n">
         <v>0</v>
       </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -9487,6 +10555,16 @@
       <c r="S153" t="n">
         <v>0</v>
       </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -9546,6 +10624,16 @@
       <c r="S154" t="n">
         <v>0</v>
       </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -9605,6 +10693,12 @@
       <c r="S155" t="n">
         <v>0</v>
       </c>
+      <c r="T155" t="n">
+        <v>100</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -9664,6 +10758,16 @@
       <c r="S156" t="n">
         <v>0</v>
       </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -9723,6 +10827,12 @@
       <c r="S157" t="n">
         <v>0</v>
       </c>
+      <c r="T157" t="n">
+        <v>100</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -9782,6 +10892,12 @@
       <c r="S158" t="n">
         <v>0</v>
       </c>
+      <c r="T158" t="n">
+        <v>100</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -9841,6 +10957,12 @@
       <c r="S159" t="n">
         <v>0</v>
       </c>
+      <c r="T159" t="n">
+        <v>75</v>
+      </c>
+      <c r="U159" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -9900,6 +11022,12 @@
       <c r="S160" t="n">
         <v>0</v>
       </c>
+      <c r="T160" t="n">
+        <v>100</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -9959,6 +11087,12 @@
       <c r="S161" t="n">
         <v>0</v>
       </c>
+      <c r="T161" t="n">
+        <v>50</v>
+      </c>
+      <c r="U161" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -10018,6 +11152,12 @@
       <c r="S162" t="n">
         <v>0</v>
       </c>
+      <c r="T162" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U162" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -10077,6 +11217,12 @@
       <c r="S163" t="n">
         <v>0</v>
       </c>
+      <c r="T163" t="n">
+        <v>100</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -10136,6 +11282,12 @@
       <c r="S164" t="n">
         <v>0</v>
       </c>
+      <c r="T164" t="n">
+        <v>100</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -10195,6 +11347,12 @@
       <c r="S165" t="n">
         <v>0</v>
       </c>
+      <c r="T165" t="n">
+        <v>100</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -10254,6 +11412,12 @@
       <c r="S166" t="n">
         <v>0</v>
       </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -10313,6 +11477,12 @@
       <c r="S167" t="n">
         <v>0</v>
       </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -10372,6 +11542,12 @@
       <c r="S168" t="n">
         <v>0</v>
       </c>
+      <c r="T168" t="n">
+        <v>100</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -10431,6 +11607,12 @@
       <c r="S169" t="n">
         <v>0</v>
       </c>
+      <c r="T169" t="n">
+        <v>100</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -10490,6 +11672,12 @@
       <c r="S170" t="n">
         <v>0</v>
       </c>
+      <c r="T170" t="n">
+        <v>100</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -10549,6 +11737,12 @@
       <c r="S171" t="n">
         <v>0</v>
       </c>
+      <c r="T171" t="n">
+        <v>100</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -10608,6 +11802,12 @@
       <c r="S172" t="n">
         <v>0</v>
       </c>
+      <c r="T172" t="n">
+        <v>100</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -10667,6 +11867,12 @@
       <c r="S173" t="n">
         <v>0</v>
       </c>
+      <c r="T173" t="n">
+        <v>100</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -10726,6 +11932,16 @@
       <c r="S174" t="n">
         <v>0</v>
       </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -10785,6 +12001,12 @@
       <c r="S175" t="n">
         <v>0</v>
       </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -10844,6 +12066,12 @@
       <c r="S176" t="n">
         <v>0</v>
       </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -10903,6 +12131,12 @@
       <c r="S177" t="n">
         <v>0</v>
       </c>
+      <c r="T177" t="n">
+        <v>100</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -10962,6 +12196,12 @@
       <c r="S178" t="n">
         <v>0</v>
       </c>
+      <c r="T178" t="n">
+        <v>100</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -11021,6 +12261,12 @@
       <c r="S179" t="n">
         <v>0</v>
       </c>
+      <c r="T179" t="n">
+        <v>100</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -11080,6 +12326,12 @@
       <c r="S180" t="n">
         <v>0</v>
       </c>
+      <c r="T180" t="n">
+        <v>100</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -11139,6 +12391,12 @@
       <c r="S181" t="n">
         <v>0</v>
       </c>
+      <c r="T181" t="n">
+        <v>100</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -11198,6 +12456,12 @@
       <c r="S182" t="n">
         <v>0</v>
       </c>
+      <c r="T182" t="n">
+        <v>100</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -11257,6 +12521,12 @@
       <c r="S183" t="n">
         <v>0</v>
       </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -11316,6 +12586,16 @@
       <c r="S184" t="n">
         <v>0</v>
       </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -11375,6 +12655,16 @@
       <c r="S185" t="n">
         <v>0</v>
       </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -11434,6 +12724,16 @@
       <c r="S186" t="n">
         <v>0</v>
       </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -11493,6 +12793,16 @@
       <c r="S187" t="n">
         <v>0</v>
       </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -11552,6 +12862,16 @@
       <c r="S188" t="n">
         <v>1</v>
       </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -11611,6 +12931,12 @@
       <c r="S189" t="n">
         <v>3</v>
       </c>
+      <c r="T189" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U189" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -11670,6 +12996,16 @@
       <c r="S190" t="n">
         <v>0</v>
       </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -11729,6 +13065,12 @@
       <c r="S191" t="n">
         <v>0</v>
       </c>
+      <c r="T191" t="n">
+        <v>100</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -11788,6 +13130,16 @@
       <c r="S192" t="n">
         <v>0</v>
       </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -11847,6 +13199,12 @@
       <c r="S193" t="n">
         <v>0</v>
       </c>
+      <c r="T193" t="n">
+        <v>50</v>
+      </c>
+      <c r="U193" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -11906,6 +13264,12 @@
       <c r="S194" t="n">
         <v>0</v>
       </c>
+      <c r="T194" t="n">
+        <v>100</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -11965,6 +13329,12 @@
       <c r="S195" t="n">
         <v>0</v>
       </c>
+      <c r="T195" t="n">
+        <v>100</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -12024,6 +13394,12 @@
       <c r="S196" t="n">
         <v>0</v>
       </c>
+      <c r="T196" t="n">
+        <v>100</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -12083,6 +13459,16 @@
       <c r="S197" t="n">
         <v>0</v>
       </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -12142,6 +13528,12 @@
       <c r="S198" t="n">
         <v>0</v>
       </c>
+      <c r="T198" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U198" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -12201,6 +13593,12 @@
       <c r="S199" t="n">
         <v>0</v>
       </c>
+      <c r="T199" t="n">
+        <v>75</v>
+      </c>
+      <c r="U199" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -12260,6 +13658,12 @@
       <c r="S200" t="n">
         <v>0</v>
       </c>
+      <c r="T200" t="n">
+        <v>80</v>
+      </c>
+      <c r="U200" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -12319,6 +13723,12 @@
       <c r="S201" t="n">
         <v>0</v>
       </c>
+      <c r="T201" t="n">
+        <v>75</v>
+      </c>
+      <c r="U201" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -12378,6 +13788,12 @@
       <c r="S202" t="n">
         <v>0</v>
       </c>
+      <c r="T202" t="n">
+        <v>75</v>
+      </c>
+      <c r="U202" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -12437,6 +13853,12 @@
       <c r="S203" t="n">
         <v>0</v>
       </c>
+      <c r="T203" t="n">
+        <v>100</v>
+      </c>
+      <c r="U203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -12496,6 +13918,12 @@
       <c r="S204" t="n">
         <v>0</v>
       </c>
+      <c r="T204" t="n">
+        <v>100</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -12555,6 +13983,12 @@
       <c r="S205" t="n">
         <v>0</v>
       </c>
+      <c r="T205" t="n">
+        <v>100</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -12614,6 +14048,12 @@
       <c r="S206" t="n">
         <v>0</v>
       </c>
+      <c r="T206" t="n">
+        <v>50</v>
+      </c>
+      <c r="U206" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -12673,6 +14113,12 @@
       <c r="S207" t="n">
         <v>0</v>
       </c>
+      <c r="T207" t="n">
+        <v>100</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -12732,6 +14178,12 @@
       <c r="S208" t="n">
         <v>0</v>
       </c>
+      <c r="T208" t="n">
+        <v>100</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -12791,6 +14243,12 @@
       <c r="S209" t="n">
         <v>0</v>
       </c>
+      <c r="T209" t="n">
+        <v>100</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -12850,6 +14308,12 @@
       <c r="S210" t="n">
         <v>0</v>
       </c>
+      <c r="T210" t="n">
+        <v>100</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -12909,6 +14373,12 @@
       <c r="S211" t="n">
         <v>1</v>
       </c>
+      <c r="T211" t="n">
+        <v>100</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -12968,6 +14438,12 @@
       <c r="S212" t="n">
         <v>0</v>
       </c>
+      <c r="T212" t="n">
+        <v>100</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -13027,6 +14503,12 @@
       <c r="S213" t="n">
         <v>0</v>
       </c>
+      <c r="T213" t="n">
+        <v>100</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -13086,6 +14568,12 @@
       <c r="S214" t="n">
         <v>0</v>
       </c>
+      <c r="T214" t="n">
+        <v>100</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -13145,6 +14633,12 @@
       <c r="S215" t="n">
         <v>0</v>
       </c>
+      <c r="T215" t="n">
+        <v>100</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -13204,6 +14698,12 @@
       <c r="S216" t="n">
         <v>0</v>
       </c>
+      <c r="T216" t="n">
+        <v>100</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -13263,6 +14763,12 @@
       <c r="S217" t="n">
         <v>0</v>
       </c>
+      <c r="T217" t="n">
+        <v>100</v>
+      </c>
+      <c r="U217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -13322,6 +14828,12 @@
       <c r="S218" t="n">
         <v>0</v>
       </c>
+      <c r="T218" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U218" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -13381,6 +14893,12 @@
       <c r="S219" t="n">
         <v>0</v>
       </c>
+      <c r="T219" t="n">
+        <v>100</v>
+      </c>
+      <c r="U219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -13440,6 +14958,12 @@
       <c r="S220" t="n">
         <v>0</v>
       </c>
+      <c r="T220" t="n">
+        <v>100</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -13499,6 +15023,12 @@
       <c r="S221" t="n">
         <v>0</v>
       </c>
+      <c r="T221" t="n">
+        <v>50</v>
+      </c>
+      <c r="U221" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -13558,6 +15088,12 @@
       <c r="S222" t="n">
         <v>0</v>
       </c>
+      <c r="T222" t="n">
+        <v>100</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -13617,6 +15153,12 @@
       <c r="S223" t="n">
         <v>0</v>
       </c>
+      <c r="T223" t="n">
+        <v>100</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -13676,6 +15218,12 @@
       <c r="S224" t="n">
         <v>0</v>
       </c>
+      <c r="T224" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U224" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -13735,6 +15283,12 @@
       <c r="S225" t="n">
         <v>0</v>
       </c>
+      <c r="T225" t="n">
+        <v>75</v>
+      </c>
+      <c r="U225" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -13794,6 +15348,12 @@
       <c r="S226" t="n">
         <v>0</v>
       </c>
+      <c r="T226" t="n">
+        <v>75</v>
+      </c>
+      <c r="U226" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -13853,6 +15413,12 @@
       <c r="S227" t="n">
         <v>0</v>
       </c>
+      <c r="T227" t="n">
+        <v>100</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -13912,6 +15478,16 @@
       <c r="S228" t="n">
         <v>0</v>
       </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -13971,6 +15547,16 @@
       <c r="S229" t="n">
         <v>0</v>
       </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -14030,6 +15616,16 @@
       <c r="S230" t="n">
         <v>1</v>
       </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -14089,6 +15685,12 @@
       <c r="S231" t="n">
         <v>0</v>
       </c>
+      <c r="T231" t="n">
+        <v>100</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -14148,6 +15750,12 @@
       <c r="S232" t="n">
         <v>0</v>
       </c>
+      <c r="T232" t="n">
+        <v>100</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -14207,6 +15815,12 @@
       <c r="S233" t="n">
         <v>0</v>
       </c>
+      <c r="T233" t="n">
+        <v>100</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -14266,6 +15880,16 @@
       <c r="S234" t="n">
         <v>1</v>
       </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -14325,6 +15949,12 @@
       <c r="S235" t="n">
         <v>0</v>
       </c>
+      <c r="T235" t="n">
+        <v>50</v>
+      </c>
+      <c r="U235" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -14384,6 +16014,12 @@
       <c r="S236" t="n">
         <v>0</v>
       </c>
+      <c r="T236" t="n">
+        <v>100</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -14443,6 +16079,12 @@
       <c r="S237" t="n">
         <v>0</v>
       </c>
+      <c r="T237" t="n">
+        <v>100</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -14502,6 +16144,12 @@
       <c r="S238" t="n">
         <v>0</v>
       </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -14561,6 +16209,12 @@
       <c r="S239" t="n">
         <v>0</v>
       </c>
+      <c r="T239" t="n">
+        <v>50</v>
+      </c>
+      <c r="U239" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -14620,6 +16274,16 @@
       <c r="S240" t="n">
         <v>1</v>
       </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -14679,6 +16343,12 @@
       <c r="S241" t="n">
         <v>0</v>
       </c>
+      <c r="T241" t="n">
+        <v>100</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -14738,6 +16408,12 @@
       <c r="S242" t="n">
         <v>1</v>
       </c>
+      <c r="T242" t="n">
+        <v>100</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -14797,6 +16473,12 @@
       <c r="S243" t="n">
         <v>0</v>
       </c>
+      <c r="T243" t="n">
+        <v>100</v>
+      </c>
+      <c r="U243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -14856,6 +16538,12 @@
       <c r="S244" t="n">
         <v>0</v>
       </c>
+      <c r="T244" t="n">
+        <v>100</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -14915,6 +16603,12 @@
       <c r="S245" t="n">
         <v>0</v>
       </c>
+      <c r="T245" t="n">
+        <v>60</v>
+      </c>
+      <c r="U245" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -14974,6 +16668,16 @@
       <c r="S246" t="n">
         <v>0</v>
       </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -15033,6 +16737,16 @@
       <c r="S247" t="n">
         <v>0</v>
       </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -15092,6 +16806,16 @@
       <c r="S248" t="n">
         <v>0</v>
       </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -15151,6 +16875,16 @@
       <c r="S249" t="n">
         <v>0</v>
       </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -15210,6 +16944,16 @@
       <c r="S250" t="n">
         <v>0</v>
       </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -15269,6 +17013,16 @@
       <c r="S251" t="n">
         <v>0</v>
       </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -15328,6 +17082,12 @@
       <c r="S252" t="n">
         <v>0</v>
       </c>
+      <c r="T252" t="n">
+        <v>50</v>
+      </c>
+      <c r="U252" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -15387,6 +17147,12 @@
       <c r="S253" t="n">
         <v>0</v>
       </c>
+      <c r="T253" t="n">
+        <v>50</v>
+      </c>
+      <c r="U253" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -15446,6 +17212,12 @@
       <c r="S254" t="n">
         <v>0</v>
       </c>
+      <c r="T254" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U254" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -15505,6 +17277,12 @@
       <c r="S255" t="n">
         <v>0</v>
       </c>
+      <c r="T255" t="n">
+        <v>100</v>
+      </c>
+      <c r="U255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -15564,6 +17342,16 @@
       <c r="S256" t="n">
         <v>0</v>
       </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -15623,6 +17411,12 @@
       <c r="S257" t="n">
         <v>0</v>
       </c>
+      <c r="T257" t="n">
+        <v>100</v>
+      </c>
+      <c r="U257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -15682,6 +17476,12 @@
       <c r="S258" t="n">
         <v>0</v>
       </c>
+      <c r="T258" t="n">
+        <v>100</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -15741,6 +17541,12 @@
       <c r="S259" t="n">
         <v>0</v>
       </c>
+      <c r="T259" t="n">
+        <v>100</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -15800,6 +17606,16 @@
       <c r="S260" t="n">
         <v>1</v>
       </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -15859,6 +17675,16 @@
       <c r="S261" t="n">
         <v>0</v>
       </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -15918,6 +17744,12 @@
       <c r="S262" t="n">
         <v>0</v>
       </c>
+      <c r="T262" t="n">
+        <v>100</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -15977,6 +17809,12 @@
       <c r="S263" t="n">
         <v>1</v>
       </c>
+      <c r="T263" t="n">
+        <v>100</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -16036,6 +17874,16 @@
       <c r="S264" t="n">
         <v>0</v>
       </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -16095,6 +17943,16 @@
       <c r="S265" t="n">
         <v>0</v>
       </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -16154,6 +18012,12 @@
       <c r="S266" t="n">
         <v>0</v>
       </c>
+      <c r="T266" t="n">
+        <v>100</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -16213,6 +18077,12 @@
       <c r="S267" t="n">
         <v>0</v>
       </c>
+      <c r="T267" t="n">
+        <v>100</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -16272,6 +18142,16 @@
       <c r="S268" t="n">
         <v>0</v>
       </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -16331,6 +18211,12 @@
       <c r="S269" t="n">
         <v>0</v>
       </c>
+      <c r="T269" t="n">
+        <v>100</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -16390,6 +18276,12 @@
       <c r="S270" t="n">
         <v>0</v>
       </c>
+      <c r="T270" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U270" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -16449,6 +18341,16 @@
       <c r="S271" t="n">
         <v>1</v>
       </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -16508,6 +18410,16 @@
       <c r="S272" t="n">
         <v>0</v>
       </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -16567,6 +18479,12 @@
       <c r="S273" t="n">
         <v>0</v>
       </c>
+      <c r="T273" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U273" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -16626,6 +18544,12 @@
       <c r="S274" t="n">
         <v>0</v>
       </c>
+      <c r="T274" t="n">
+        <v>50</v>
+      </c>
+      <c r="U274" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -16685,6 +18609,12 @@
       <c r="S275" t="n">
         <v>0</v>
       </c>
+      <c r="T275" t="n">
+        <v>75</v>
+      </c>
+      <c r="U275" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -16744,6 +18674,16 @@
       <c r="S276" t="n">
         <v>0</v>
       </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -16803,6 +18743,16 @@
       <c r="S277" t="n">
         <v>0</v>
       </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -16862,6 +18812,12 @@
       <c r="S278" t="n">
         <v>0</v>
       </c>
+      <c r="T278" t="n">
+        <v>50</v>
+      </c>
+      <c r="U278" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -16921,6 +18877,12 @@
       <c r="S279" t="n">
         <v>0</v>
       </c>
+      <c r="T279" t="n">
+        <v>100</v>
+      </c>
+      <c r="U279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -16980,6 +18942,12 @@
       <c r="S280" t="n">
         <v>0</v>
       </c>
+      <c r="T280" t="n">
+        <v>100</v>
+      </c>
+      <c r="U280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -17039,6 +19007,12 @@
       <c r="S281" t="n">
         <v>0</v>
       </c>
+      <c r="T281" t="n">
+        <v>75</v>
+      </c>
+      <c r="U281" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -17098,6 +19072,12 @@
       <c r="S282" t="n">
         <v>0</v>
       </c>
+      <c r="T282" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U282" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -17157,6 +19137,12 @@
       <c r="S283" t="n">
         <v>0</v>
       </c>
+      <c r="T283" t="n">
+        <v>100</v>
+      </c>
+      <c r="U283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -17216,6 +19202,12 @@
       <c r="S284" t="n">
         <v>0</v>
       </c>
+      <c r="T284" t="n">
+        <v>100</v>
+      </c>
+      <c r="U284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -17275,6 +19267,16 @@
       <c r="S285" t="n">
         <v>1</v>
       </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -17334,6 +19336,12 @@
       <c r="S286" t="n">
         <v>0</v>
       </c>
+      <c r="T286" t="n">
+        <v>100</v>
+      </c>
+      <c r="U286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -17393,6 +19401,16 @@
       <c r="S287" t="n">
         <v>0</v>
       </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -17452,6 +19470,12 @@
       <c r="S288" t="n">
         <v>0</v>
       </c>
+      <c r="T288" t="n">
+        <v>100</v>
+      </c>
+      <c r="U288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -17511,6 +19535,12 @@
       <c r="S289" t="n">
         <v>0</v>
       </c>
+      <c r="T289" t="n">
+        <v>100</v>
+      </c>
+      <c r="U289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -17570,6 +19600,12 @@
       <c r="S290" t="n">
         <v>0</v>
       </c>
+      <c r="T290" t="n">
+        <v>50</v>
+      </c>
+      <c r="U290" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -17629,6 +19665,12 @@
       <c r="S291" t="n">
         <v>0</v>
       </c>
+      <c r="T291" t="n">
+        <v>100</v>
+      </c>
+      <c r="U291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -17688,6 +19730,16 @@
       <c r="S292" t="n">
         <v>0</v>
       </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -17747,6 +19799,12 @@
       <c r="S293" t="n">
         <v>0</v>
       </c>
+      <c r="T293" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U293" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -17806,6 +19864,16 @@
       <c r="S294" t="n">
         <v>0</v>
       </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -17865,6 +19933,12 @@
       <c r="S295" t="n">
         <v>0</v>
       </c>
+      <c r="T295" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U295" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -17924,6 +19998,12 @@
       <c r="S296" t="n">
         <v>0</v>
       </c>
+      <c r="T296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -17983,6 +20063,12 @@
       <c r="S297" t="n">
         <v>0</v>
       </c>
+      <c r="T297" t="n">
+        <v>100</v>
+      </c>
+      <c r="U297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -18042,6 +20128,12 @@
       <c r="S298" t="n">
         <v>0</v>
       </c>
+      <c r="T298" t="n">
+        <v>100</v>
+      </c>
+      <c r="U298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -18101,6 +20193,12 @@
       <c r="S299" t="n">
         <v>0</v>
       </c>
+      <c r="T299" t="n">
+        <v>100</v>
+      </c>
+      <c r="U299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -18160,6 +20258,12 @@
       <c r="S300" t="n">
         <v>0</v>
       </c>
+      <c r="T300" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U300" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -18219,6 +20323,12 @@
       <c r="S301" t="n">
         <v>2</v>
       </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -18278,6 +20388,12 @@
       <c r="S302" t="n">
         <v>0</v>
       </c>
+      <c r="T302" t="n">
+        <v>73.3333333333333</v>
+      </c>
+      <c r="U302" t="n">
+        <v>26.6666666666666</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -18337,6 +20453,12 @@
       <c r="S303" t="n">
         <v>0</v>
       </c>
+      <c r="T303" t="n">
+        <v>100</v>
+      </c>
+      <c r="U303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -18396,6 +20518,16 @@
       <c r="S304" t="n">
         <v>0</v>
       </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -18455,6 +20587,16 @@
       <c r="S305" t="n">
         <v>0</v>
       </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -18514,6 +20656,16 @@
       <c r="S306" t="n">
         <v>0</v>
       </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -18573,6 +20725,12 @@
       <c r="S307" t="n">
         <v>0</v>
       </c>
+      <c r="T307" t="n">
+        <v>80</v>
+      </c>
+      <c r="U307" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -18632,6 +20790,16 @@
       <c r="S308" t="n">
         <v>0</v>
       </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -18691,6 +20859,16 @@
       <c r="S309" t="n">
         <v>0</v>
       </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -18750,6 +20928,16 @@
       <c r="S310" t="n">
         <v>0</v>
       </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -18809,6 +20997,12 @@
       <c r="S311" t="n">
         <v>0</v>
       </c>
+      <c r="T311" t="n">
+        <v>100</v>
+      </c>
+      <c r="U311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
@@ -18868,6 +21062,12 @@
       <c r="S312" t="n">
         <v>0</v>
       </c>
+      <c r="T312" t="n">
+        <v>100</v>
+      </c>
+      <c r="U312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
@@ -18927,6 +21127,12 @@
       <c r="S313" t="n">
         <v>2</v>
       </c>
+      <c r="T313" t="n">
+        <v>50</v>
+      </c>
+      <c r="U313" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
@@ -18986,6 +21192,16 @@
       <c r="S314" t="n">
         <v>1</v>
       </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
@@ -19045,6 +21261,12 @@
       <c r="S315" t="n">
         <v>0</v>
       </c>
+      <c r="T315" t="n">
+        <v>100</v>
+      </c>
+      <c r="U315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
@@ -19104,6 +21326,12 @@
       <c r="S316" t="n">
         <v>0</v>
       </c>
+      <c r="T316" t="n">
+        <v>100</v>
+      </c>
+      <c r="U316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -19163,6 +21391,12 @@
       <c r="S317" t="n">
         <v>0</v>
       </c>
+      <c r="T317" t="n">
+        <v>100</v>
+      </c>
+      <c r="U317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -19222,6 +21456,16 @@
       <c r="S318" t="n">
         <v>0</v>
       </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -19281,6 +21525,12 @@
       <c r="S319" t="n">
         <v>0</v>
       </c>
+      <c r="T319" t="n">
+        <v>100</v>
+      </c>
+      <c r="U319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -19340,6 +21590,12 @@
       <c r="S320" t="n">
         <v>0</v>
       </c>
+      <c r="T320" t="n">
+        <v>100</v>
+      </c>
+      <c r="U320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -19399,6 +21655,12 @@
       <c r="S321" t="n">
         <v>0</v>
       </c>
+      <c r="T321" t="n">
+        <v>100</v>
+      </c>
+      <c r="U321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -19458,6 +21720,12 @@
       <c r="S322" t="n">
         <v>0</v>
       </c>
+      <c r="T322" t="n">
+        <v>100</v>
+      </c>
+      <c r="U322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -19517,6 +21785,12 @@
       <c r="S323" t="n">
         <v>0</v>
       </c>
+      <c r="T323" t="n">
+        <v>100</v>
+      </c>
+      <c r="U323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -19576,6 +21850,12 @@
       <c r="S324" t="n">
         <v>1</v>
       </c>
+      <c r="T324" t="n">
+        <v>100</v>
+      </c>
+      <c r="U324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -19635,6 +21915,16 @@
       <c r="S325" t="n">
         <v>0</v>
       </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -19694,6 +21984,12 @@
       <c r="S326" t="n">
         <v>0</v>
       </c>
+      <c r="T326" t="n">
+        <v>100</v>
+      </c>
+      <c r="U326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -19753,6 +22049,12 @@
       <c r="S327" t="n">
         <v>0</v>
       </c>
+      <c r="T327" t="n">
+        <v>100</v>
+      </c>
+      <c r="U327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -19812,6 +22114,12 @@
       <c r="S328" t="n">
         <v>0</v>
       </c>
+      <c r="T328" t="n">
+        <v>100</v>
+      </c>
+      <c r="U328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -19871,6 +22179,12 @@
       <c r="S329" t="n">
         <v>0</v>
       </c>
+      <c r="T329" t="n">
+        <v>100</v>
+      </c>
+      <c r="U329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -19930,6 +22244,12 @@
       <c r="S330" t="n">
         <v>0</v>
       </c>
+      <c r="T330" t="n">
+        <v>50</v>
+      </c>
+      <c r="U330" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -19989,6 +22309,12 @@
       <c r="S331" t="n">
         <v>0</v>
       </c>
+      <c r="T331" t="n">
+        <v>100</v>
+      </c>
+      <c r="U331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -20048,6 +22374,12 @@
       <c r="S332" t="n">
         <v>0</v>
       </c>
+      <c r="T332" t="n">
+        <v>50</v>
+      </c>
+      <c r="U332" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -20107,6 +22439,12 @@
       <c r="S333" t="n">
         <v>0</v>
       </c>
+      <c r="T333" t="n">
+        <v>50</v>
+      </c>
+      <c r="U333" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -20166,6 +22504,12 @@
       <c r="S334" t="n">
         <v>0</v>
       </c>
+      <c r="T334" t="n">
+        <v>0</v>
+      </c>
+      <c r="U334" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -20225,6 +22569,12 @@
       <c r="S335" t="n">
         <v>0</v>
       </c>
+      <c r="T335" t="n">
+        <v>50</v>
+      </c>
+      <c r="U335" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -20284,6 +22634,12 @@
       <c r="S336" t="n">
         <v>0</v>
       </c>
+      <c r="T336" t="n">
+        <v>100</v>
+      </c>
+      <c r="U336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -20343,6 +22699,12 @@
       <c r="S337" t="n">
         <v>0</v>
       </c>
+      <c r="T337" t="n">
+        <v>100</v>
+      </c>
+      <c r="U337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -20402,6 +22764,16 @@
       <c r="S338" t="n">
         <v>0</v>
       </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -20461,6 +22833,16 @@
       <c r="S339" t="n">
         <v>1</v>
       </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -20520,6 +22902,12 @@
       <c r="S340" t="n">
         <v>0</v>
       </c>
+      <c r="T340" t="n">
+        <v>50</v>
+      </c>
+      <c r="U340" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -20579,6 +22967,12 @@
       <c r="S341" t="n">
         <v>0</v>
       </c>
+      <c r="T341" t="n">
+        <v>100</v>
+      </c>
+      <c r="U341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -20638,6 +23032,12 @@
       <c r="S342" t="n">
         <v>1</v>
       </c>
+      <c r="T342" t="n">
+        <v>100</v>
+      </c>
+      <c r="U342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -20697,6 +23097,16 @@
       <c r="S343" t="n">
         <v>0</v>
       </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -20756,6 +23166,16 @@
       <c r="S344" t="n">
         <v>0</v>
       </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -20815,6 +23235,12 @@
       <c r="S345" t="n">
         <v>0</v>
       </c>
+      <c r="T345" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U345" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -20874,6 +23300,12 @@
       <c r="S346" t="n">
         <v>0</v>
       </c>
+      <c r="T346" t="n">
+        <v>100</v>
+      </c>
+      <c r="U346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -20933,6 +23365,12 @@
       <c r="S347" t="n">
         <v>0</v>
       </c>
+      <c r="T347" t="n">
+        <v>100</v>
+      </c>
+      <c r="U347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -20992,6 +23430,12 @@
       <c r="S348" t="n">
         <v>0</v>
       </c>
+      <c r="T348" t="n">
+        <v>75</v>
+      </c>
+      <c r="U348" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -21051,6 +23495,12 @@
       <c r="S349" t="n">
         <v>0</v>
       </c>
+      <c r="T349" t="n">
+        <v>100</v>
+      </c>
+      <c r="U349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -21110,6 +23560,12 @@
       <c r="S350" t="n">
         <v>0</v>
       </c>
+      <c r="T350" t="n">
+        <v>100</v>
+      </c>
+      <c r="U350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -21169,6 +23625,12 @@
       <c r="S351" t="n">
         <v>0</v>
       </c>
+      <c r="T351" t="n">
+        <v>100</v>
+      </c>
+      <c r="U351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -21228,6 +23690,12 @@
       <c r="S352" t="n">
         <v>0</v>
       </c>
+      <c r="T352" t="n">
+        <v>100</v>
+      </c>
+      <c r="U352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -21287,6 +23755,12 @@
       <c r="S353" t="n">
         <v>1</v>
       </c>
+      <c r="T353" t="n">
+        <v>100</v>
+      </c>
+      <c r="U353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -21346,6 +23820,12 @@
       <c r="S354" t="n">
         <v>0</v>
       </c>
+      <c r="T354" t="n">
+        <v>80</v>
+      </c>
+      <c r="U354" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -21405,6 +23885,12 @@
       <c r="S355" t="n">
         <v>0</v>
       </c>
+      <c r="T355" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U355" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -21464,6 +23950,12 @@
       <c r="S356" t="n">
         <v>0</v>
       </c>
+      <c r="T356" t="n">
+        <v>100</v>
+      </c>
+      <c r="U356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -21523,6 +24015,12 @@
       <c r="S357" t="n">
         <v>0</v>
       </c>
+      <c r="T357" t="n">
+        <v>100</v>
+      </c>
+      <c r="U357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -21582,6 +24080,12 @@
       <c r="S358" t="n">
         <v>0</v>
       </c>
+      <c r="T358" t="n">
+        <v>100</v>
+      </c>
+      <c r="U358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -21641,6 +24145,12 @@
       <c r="S359" t="n">
         <v>0</v>
       </c>
+      <c r="T359" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U359" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -21700,6 +24210,12 @@
       <c r="S360" t="n">
         <v>0</v>
       </c>
+      <c r="T360" t="n">
+        <v>100</v>
+      </c>
+      <c r="U360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -21759,6 +24275,12 @@
       <c r="S361" t="n">
         <v>0</v>
       </c>
+      <c r="T361" t="n">
+        <v>100</v>
+      </c>
+      <c r="U361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -21818,6 +24340,16 @@
       <c r="S362" t="n">
         <v>0</v>
       </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -21877,6 +24409,16 @@
       <c r="S363" t="n">
         <v>0</v>
       </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -21936,6 +24478,16 @@
       <c r="S364" t="n">
         <v>0</v>
       </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -21995,6 +24547,16 @@
       <c r="S365" t="n">
         <v>0</v>
       </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -22054,6 +24616,16 @@
       <c r="S366" t="n">
         <v>0</v>
       </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -22113,6 +24685,16 @@
       <c r="S367" t="n">
         <v>0</v>
       </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -22172,6 +24754,16 @@
       <c r="S368" t="n">
         <v>0</v>
       </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -22231,6 +24823,16 @@
       <c r="S369" t="n">
         <v>0</v>
       </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -22290,6 +24892,16 @@
       <c r="S370" t="n">
         <v>0</v>
       </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -22349,6 +24961,16 @@
       <c r="S371" t="n">
         <v>0</v>
       </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -22408,6 +25030,16 @@
       <c r="S372" t="n">
         <v>0</v>
       </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -22467,6 +25099,16 @@
       <c r="S373" t="n">
         <v>0</v>
       </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -22526,6 +25168,16 @@
       <c r="S374" t="n">
         <v>0</v>
       </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -22585,6 +25237,16 @@
       <c r="S375" t="n">
         <v>0</v>
       </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -22644,6 +25306,16 @@
       <c r="S376" t="n">
         <v>0</v>
       </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -22703,6 +25375,16 @@
       <c r="S377" t="n">
         <v>0</v>
       </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -22762,6 +25444,16 @@
       <c r="S378" t="n">
         <v>0</v>
       </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -22821,6 +25513,16 @@
       <c r="S379" t="n">
         <v>0</v>
       </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -22880,6 +25582,16 @@
       <c r="S380" t="n">
         <v>0</v>
       </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -22939,6 +25651,16 @@
       <c r="S381" t="n">
         <v>0</v>
       </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -22998,6 +25720,16 @@
       <c r="S382" t="n">
         <v>0</v>
       </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -23057,6 +25789,16 @@
       <c r="S383" t="n">
         <v>0</v>
       </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -23116,6 +25858,16 @@
       <c r="S384" t="n">
         <v>0</v>
       </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -23175,6 +25927,16 @@
       <c r="S385" t="n">
         <v>0</v>
       </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -23234,6 +25996,16 @@
       <c r="S386" t="n">
         <v>1</v>
       </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -23293,6 +26065,16 @@
       <c r="S387" t="n">
         <v>1</v>
       </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -23352,6 +26134,16 @@
       <c r="S388" t="n">
         <v>0</v>
       </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -23411,6 +26203,16 @@
       <c r="S389" t="n">
         <v>2</v>
       </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -23470,6 +26272,16 @@
       <c r="S390" t="n">
         <v>0</v>
       </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -23529,6 +26341,16 @@
       <c r="S391" t="n">
         <v>0</v>
       </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -23588,6 +26410,16 @@
       <c r="S392" t="n">
         <v>0</v>
       </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -23647,6 +26479,16 @@
       <c r="S393" t="n">
         <v>0</v>
       </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -23706,6 +26548,12 @@
       <c r="S394" t="n">
         <v>0</v>
       </c>
+      <c r="T394" t="n">
+        <v>50</v>
+      </c>
+      <c r="U394" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -23765,6 +26613,12 @@
       <c r="S395" t="n">
         <v>0</v>
       </c>
+      <c r="T395" t="n">
+        <v>100</v>
+      </c>
+      <c r="U395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -23824,6 +26678,12 @@
       <c r="S396" t="n">
         <v>0</v>
       </c>
+      <c r="T396" t="n">
+        <v>100</v>
+      </c>
+      <c r="U396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -23883,6 +26743,12 @@
       <c r="S397" t="n">
         <v>0</v>
       </c>
+      <c r="T397" t="n">
+        <v>100</v>
+      </c>
+      <c r="U397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -23942,6 +26808,12 @@
       <c r="S398" t="n">
         <v>0</v>
       </c>
+      <c r="T398" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U398" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -24001,6 +26873,12 @@
       <c r="S399" t="n">
         <v>0</v>
       </c>
+      <c r="T399" t="n">
+        <v>100</v>
+      </c>
+      <c r="U399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -24060,6 +26938,12 @@
       <c r="S400" t="n">
         <v>1</v>
       </c>
+      <c r="T400" t="n">
+        <v>100</v>
+      </c>
+      <c r="U400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -24119,6 +27003,12 @@
       <c r="S401" t="n">
         <v>0</v>
       </c>
+      <c r="T401" t="n">
+        <v>50</v>
+      </c>
+      <c r="U401" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -24178,6 +27068,12 @@
       <c r="S402" t="n">
         <v>0</v>
       </c>
+      <c r="T402" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U402" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -24237,6 +27133,12 @@
       <c r="S403" t="n">
         <v>0</v>
       </c>
+      <c r="T403" t="n">
+        <v>100</v>
+      </c>
+      <c r="U403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -24296,6 +27198,12 @@
       <c r="S404" t="n">
         <v>1</v>
       </c>
+      <c r="T404" t="n">
+        <v>75</v>
+      </c>
+      <c r="U404" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -24355,6 +27263,12 @@
       <c r="S405" t="n">
         <v>0</v>
       </c>
+      <c r="T405" t="n">
+        <v>100</v>
+      </c>
+      <c r="U405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -24414,6 +27328,12 @@
       <c r="S406" t="n">
         <v>0</v>
       </c>
+      <c r="T406" t="n">
+        <v>100</v>
+      </c>
+      <c r="U406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -24473,6 +27393,16 @@
       <c r="S407" t="n">
         <v>0</v>
       </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -24532,6 +27462,12 @@
       <c r="S408" t="n">
         <v>0</v>
       </c>
+      <c r="T408" t="n">
+        <v>100</v>
+      </c>
+      <c r="U408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -24591,6 +27527,12 @@
       <c r="S409" t="n">
         <v>0</v>
       </c>
+      <c r="T409" t="n">
+        <v>100</v>
+      </c>
+      <c r="U409" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -24650,6 +27592,12 @@
       <c r="S410" t="n">
         <v>0</v>
       </c>
+      <c r="T410" t="n">
+        <v>100</v>
+      </c>
+      <c r="U410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -24709,6 +27657,12 @@
       <c r="S411" t="n">
         <v>0</v>
       </c>
+      <c r="T411" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U411" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -24768,6 +27722,12 @@
       <c r="S412" t="n">
         <v>0</v>
       </c>
+      <c r="T412" t="n">
+        <v>100</v>
+      </c>
+      <c r="U412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -24827,6 +27787,12 @@
       <c r="S413" t="n">
         <v>1</v>
       </c>
+      <c r="T413" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U413" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -24886,6 +27852,12 @@
       <c r="S414" t="n">
         <v>0</v>
       </c>
+      <c r="T414" t="n">
+        <v>100</v>
+      </c>
+      <c r="U414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -24945,6 +27917,12 @@
       <c r="S415" t="n">
         <v>0</v>
       </c>
+      <c r="T415" t="n">
+        <v>60</v>
+      </c>
+      <c r="U415" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
@@ -25004,6 +27982,12 @@
       <c r="S416" t="n">
         <v>0</v>
       </c>
+      <c r="T416" t="n">
+        <v>100</v>
+      </c>
+      <c r="U416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
@@ -25063,6 +28047,12 @@
       <c r="S417" t="n">
         <v>0</v>
       </c>
+      <c r="T417" t="n">
+        <v>75</v>
+      </c>
+      <c r="U417" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
@@ -25122,6 +28112,12 @@
       <c r="S418" t="n">
         <v>0</v>
       </c>
+      <c r="T418" t="n">
+        <v>100</v>
+      </c>
+      <c r="U418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
@@ -25181,6 +28177,12 @@
       <c r="S419" t="n">
         <v>2</v>
       </c>
+      <c r="T419" t="n">
+        <v>100</v>
+      </c>
+      <c r="U419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
@@ -25240,6 +28242,12 @@
       <c r="S420" t="n">
         <v>0</v>
       </c>
+      <c r="T420" t="n">
+        <v>100</v>
+      </c>
+      <c r="U420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
@@ -25299,6 +28307,12 @@
       <c r="S421" t="n">
         <v>0</v>
       </c>
+      <c r="T421" t="n">
+        <v>100</v>
+      </c>
+      <c r="U421" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
@@ -25358,6 +28372,12 @@
       <c r="S422" t="n">
         <v>0</v>
       </c>
+      <c r="T422" t="n">
+        <v>100</v>
+      </c>
+      <c r="U422" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
@@ -25417,6 +28437,12 @@
       <c r="S423" t="n">
         <v>0</v>
       </c>
+      <c r="T423" t="n">
+        <v>100</v>
+      </c>
+      <c r="U423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
@@ -25476,6 +28502,16 @@
       <c r="S424" t="n">
         <v>0</v>
       </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
@@ -25535,6 +28571,16 @@
       <c r="S425" t="n">
         <v>0</v>
       </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
@@ -25594,6 +28640,16 @@
       <c r="S426" t="n">
         <v>0</v>
       </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
@@ -25653,6 +28709,16 @@
       <c r="S427" t="n">
         <v>0</v>
       </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
@@ -25712,6 +28778,16 @@
       <c r="S428" t="n">
         <v>0</v>
       </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
@@ -25771,6 +28847,12 @@
       <c r="S429" t="n">
         <v>0</v>
       </c>
+      <c r="T429" t="n">
+        <v>75</v>
+      </c>
+      <c r="U429" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
@@ -25830,6 +28912,12 @@
       <c r="S430" t="n">
         <v>1</v>
       </c>
+      <c r="T430" t="n">
+        <v>100</v>
+      </c>
+      <c r="U430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
@@ -25889,6 +28977,12 @@
       <c r="S431" t="n">
         <v>0</v>
       </c>
+      <c r="T431" t="n">
+        <v>100</v>
+      </c>
+      <c r="U431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
@@ -25948,6 +29042,12 @@
       <c r="S432" t="n">
         <v>0</v>
       </c>
+      <c r="T432" t="n">
+        <v>75</v>
+      </c>
+      <c r="U432" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
@@ -26007,6 +29107,12 @@
       <c r="S433" t="n">
         <v>0</v>
       </c>
+      <c r="T433" t="n">
+        <v>50</v>
+      </c>
+      <c r="U433" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
@@ -26066,6 +29172,12 @@
       <c r="S434" t="n">
         <v>0</v>
       </c>
+      <c r="T434" t="n">
+        <v>100</v>
+      </c>
+      <c r="U434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
@@ -26125,6 +29237,16 @@
       <c r="S435" t="n">
         <v>0</v>
       </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
@@ -26184,6 +29306,16 @@
       <c r="S436" t="n">
         <v>0</v>
       </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
@@ -26243,6 +29375,16 @@
       <c r="S437" t="n">
         <v>0</v>
       </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
@@ -26302,6 +29444,16 @@
       <c r="S438" t="n">
         <v>1</v>
       </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
@@ -26361,6 +29513,16 @@
       <c r="S439" t="n">
         <v>1</v>
       </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
@@ -26420,6 +29582,16 @@
       <c r="S440" t="n">
         <v>0</v>
       </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
@@ -26479,6 +29651,16 @@
       <c r="S441" t="n">
         <v>0</v>
       </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
@@ -26538,6 +29720,16 @@
       <c r="S442" t="n">
         <v>0</v>
       </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
@@ -26597,6 +29789,12 @@
       <c r="S443" t="n">
         <v>0</v>
       </c>
+      <c r="T443" t="n">
+        <v>100</v>
+      </c>
+      <c r="U443" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
@@ -26656,6 +29854,12 @@
       <c r="S444" t="n">
         <v>0</v>
       </c>
+      <c r="T444" t="n">
+        <v>100</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
@@ -26715,6 +29919,12 @@
       <c r="S445" t="n">
         <v>0</v>
       </c>
+      <c r="T445" t="n">
+        <v>50</v>
+      </c>
+      <c r="U445" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
@@ -26774,6 +29984,12 @@
       <c r="S446" t="n">
         <v>0</v>
       </c>
+      <c r="T446" t="n">
+        <v>50</v>
+      </c>
+      <c r="U446" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
@@ -26833,6 +30049,12 @@
       <c r="S447" t="n">
         <v>0</v>
       </c>
+      <c r="T447" t="n">
+        <v>100</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
@@ -26892,6 +30114,12 @@
       <c r="S448" t="n">
         <v>0</v>
       </c>
+      <c r="T448" t="n">
+        <v>100</v>
+      </c>
+      <c r="U448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
@@ -26951,6 +30179,12 @@
       <c r="S449" t="n">
         <v>0</v>
       </c>
+      <c r="T449" t="n">
+        <v>100</v>
+      </c>
+      <c r="U449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
@@ -27010,6 +30244,12 @@
       <c r="S450" t="n">
         <v>0</v>
       </c>
+      <c r="T450" t="n">
+        <v>100</v>
+      </c>
+      <c r="U450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
@@ -27069,6 +30309,16 @@
       <c r="S451" t="n">
         <v>0</v>
       </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
@@ -27128,6 +30378,12 @@
       <c r="S452" t="n">
         <v>0</v>
       </c>
+      <c r="T452" t="n">
+        <v>100</v>
+      </c>
+      <c r="U452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
@@ -27187,6 +30443,12 @@
       <c r="S453" t="n">
         <v>0</v>
       </c>
+      <c r="T453" t="n">
+        <v>0</v>
+      </c>
+      <c r="U453" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
@@ -27246,6 +30508,12 @@
       <c r="S454" t="n">
         <v>0</v>
       </c>
+      <c r="T454" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U454" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
@@ -27305,6 +30573,12 @@
       <c r="S455" t="n">
         <v>0</v>
       </c>
+      <c r="T455" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U455" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
@@ -27364,6 +30638,12 @@
       <c r="S456" t="n">
         <v>2</v>
       </c>
+      <c r="T456" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U456" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
@@ -27423,6 +30703,12 @@
       <c r="S457" t="n">
         <v>0</v>
       </c>
+      <c r="T457" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U457" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
@@ -27482,6 +30768,12 @@
       <c r="S458" t="n">
         <v>0</v>
       </c>
+      <c r="T458" t="n">
+        <v>100</v>
+      </c>
+      <c r="U458" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
@@ -27541,6 +30833,16 @@
       <c r="S459" t="n">
         <v>0</v>
       </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
@@ -27600,6 +30902,16 @@
       <c r="S460" t="n">
         <v>1</v>
       </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
@@ -27659,6 +30971,16 @@
       <c r="S461" t="n">
         <v>0</v>
       </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
@@ -27718,6 +31040,16 @@
       <c r="S462" t="n">
         <v>0</v>
       </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
@@ -27777,6 +31109,16 @@
       <c r="S463" t="n">
         <v>0</v>
       </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
@@ -27836,6 +31178,16 @@
       <c r="S464" t="n">
         <v>0</v>
       </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
@@ -27895,6 +31247,16 @@
       <c r="S465" t="n">
         <v>1</v>
       </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
@@ -27954,6 +31316,12 @@
       <c r="S466" t="n">
         <v>0</v>
       </c>
+      <c r="T466" t="n">
+        <v>100</v>
+      </c>
+      <c r="U466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
@@ -28013,6 +31381,12 @@
       <c r="S467" t="n">
         <v>4</v>
       </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
@@ -28072,6 +31446,12 @@
       <c r="S468" t="n">
         <v>0</v>
       </c>
+      <c r="T468" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U468" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
@@ -28131,6 +31511,12 @@
       <c r="S469" t="n">
         <v>0</v>
       </c>
+      <c r="T469" t="n">
+        <v>100</v>
+      </c>
+      <c r="U469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
@@ -28190,6 +31576,12 @@
       <c r="S470" t="n">
         <v>1</v>
       </c>
+      <c r="T470" t="n">
+        <v>100</v>
+      </c>
+      <c r="U470" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
@@ -28249,6 +31641,12 @@
       <c r="S471" t="n">
         <v>3</v>
       </c>
+      <c r="T471" t="n">
+        <v>75</v>
+      </c>
+      <c r="U471" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
@@ -28308,6 +31706,12 @@
       <c r="S472" t="n">
         <v>2</v>
       </c>
+      <c r="T472" t="n">
+        <v>100</v>
+      </c>
+      <c r="U472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
@@ -28367,6 +31771,12 @@
       <c r="S473" t="n">
         <v>0</v>
       </c>
+      <c r="T473" t="n">
+        <v>100</v>
+      </c>
+      <c r="U473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
@@ -28426,6 +31836,12 @@
       <c r="S474" t="n">
         <v>0</v>
       </c>
+      <c r="T474" t="n">
+        <v>75</v>
+      </c>
+      <c r="U474" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
@@ -28485,6 +31901,12 @@
       <c r="S475" t="n">
         <v>0</v>
       </c>
+      <c r="T475" t="n">
+        <v>100</v>
+      </c>
+      <c r="U475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
@@ -28544,6 +31966,16 @@
       <c r="S476" t="n">
         <v>0</v>
       </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
@@ -28603,6 +32035,16 @@
       <c r="S477" t="n">
         <v>0</v>
       </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
@@ -28662,6 +32104,16 @@
       <c r="S478" t="n">
         <v>0</v>
       </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
@@ -28721,6 +32173,16 @@
       <c r="S479" t="n">
         <v>0</v>
       </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
@@ -28780,6 +32242,12 @@
       <c r="S480" t="n">
         <v>2</v>
       </c>
+      <c r="T480" t="n">
+        <v>75</v>
+      </c>
+      <c r="U480" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
@@ -28839,6 +32307,16 @@
       <c r="S481" t="n">
         <v>0</v>
       </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
@@ -28898,6 +32376,16 @@
       <c r="S482" t="n">
         <v>0</v>
       </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
@@ -28957,6 +32445,12 @@
       <c r="S483" t="n">
         <v>0</v>
       </c>
+      <c r="T483" t="n">
+        <v>100</v>
+      </c>
+      <c r="U483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
@@ -29016,6 +32510,12 @@
       <c r="S484" t="n">
         <v>0</v>
       </c>
+      <c r="T484" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U484" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
@@ -29075,6 +32575,12 @@
       <c r="S485" t="n">
         <v>0</v>
       </c>
+      <c r="T485" t="n">
+        <v>0</v>
+      </c>
+      <c r="U485" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
@@ -29134,6 +32640,12 @@
       <c r="S486" t="n">
         <v>0</v>
       </c>
+      <c r="T486" t="n">
+        <v>100</v>
+      </c>
+      <c r="U486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
@@ -29193,6 +32705,16 @@
       <c r="S487" t="n">
         <v>0</v>
       </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
@@ -29252,6 +32774,12 @@
       <c r="S488" t="n">
         <v>0</v>
       </c>
+      <c r="T488" t="n">
+        <v>0</v>
+      </c>
+      <c r="U488" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
@@ -29311,6 +32839,12 @@
       <c r="S489" t="n">
         <v>1</v>
       </c>
+      <c r="T489" t="n">
+        <v>100</v>
+      </c>
+      <c r="U489" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
@@ -29370,6 +32904,16 @@
       <c r="S490" t="n">
         <v>1</v>
       </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
@@ -29429,6 +32973,16 @@
       <c r="S491" t="n">
         <v>0</v>
       </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
@@ -29488,6 +33042,12 @@
       <c r="S492" t="n">
         <v>1</v>
       </c>
+      <c r="T492" t="n">
+        <v>50</v>
+      </c>
+      <c r="U492" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
@@ -29547,6 +33107,16 @@
       <c r="S493" t="n">
         <v>0</v>
       </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
@@ -29606,6 +33176,16 @@
       <c r="S494" t="n">
         <v>0</v>
       </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
@@ -29665,6 +33245,16 @@
       <c r="S495" t="n">
         <v>1</v>
       </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
@@ -29724,6 +33314,12 @@
       <c r="S496" t="n">
         <v>1</v>
       </c>
+      <c r="T496" t="n">
+        <v>0</v>
+      </c>
+      <c r="U496" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
@@ -29783,6 +33379,12 @@
       <c r="S497" t="n">
         <v>0</v>
       </c>
+      <c r="T497" t="n">
+        <v>50</v>
+      </c>
+      <c r="U497" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
@@ -29842,6 +33444,12 @@
       <c r="S498" t="n">
         <v>0</v>
       </c>
+      <c r="T498" t="n">
+        <v>100</v>
+      </c>
+      <c r="U498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
@@ -29901,6 +33509,12 @@
       <c r="S499" t="n">
         <v>2</v>
       </c>
+      <c r="T499" t="n">
+        <v>50</v>
+      </c>
+      <c r="U499" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="n">
@@ -29960,6 +33574,16 @@
       <c r="S500" t="n">
         <v>0</v>
       </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="n">
@@ -30019,6 +33643,16 @@
       <c r="S501" t="n">
         <v>0</v>
       </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="1" t="n">
@@ -30078,6 +33712,16 @@
       <c r="S502" t="n">
         <v>0</v>
       </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="1" t="n">
@@ -30137,6 +33781,16 @@
       <c r="S503" t="n">
         <v>0</v>
       </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="1" t="n">
@@ -30196,6 +33850,16 @@
       <c r="S504" t="n">
         <v>0</v>
       </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="n">
@@ -30255,6 +33919,16 @@
       <c r="S505" t="n">
         <v>0</v>
       </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="1" t="n">
@@ -30314,6 +33988,16 @@
       <c r="S506" t="n">
         <v>0</v>
       </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="n">
@@ -30373,6 +34057,16 @@
       <c r="S507" t="n">
         <v>0</v>
       </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="1" t="n">
@@ -30432,6 +34126,16 @@
       <c r="S508" t="n">
         <v>0</v>
       </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="n">
@@ -30491,6 +34195,16 @@
       <c r="S509" t="n">
         <v>0</v>
       </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="n">
@@ -30550,6 +34264,16 @@
       <c r="S510" t="n">
         <v>0</v>
       </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="n">
@@ -30609,6 +34333,16 @@
       <c r="S511" t="n">
         <v>0</v>
       </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="n">
@@ -30668,6 +34402,12 @@
       <c r="S512" t="n">
         <v>0</v>
       </c>
+      <c r="T512" t="n">
+        <v>100</v>
+      </c>
+      <c r="U512" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="n">
@@ -30727,6 +34467,16 @@
       <c r="S513" t="n">
         <v>1</v>
       </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="1" t="n">
@@ -30786,6 +34536,16 @@
       <c r="S514" t="n">
         <v>0</v>
       </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="1" t="n">
@@ -30845,6 +34605,16 @@
       <c r="S515" t="n">
         <v>0</v>
       </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="n">
@@ -30904,6 +34674,16 @@
       <c r="S516" t="n">
         <v>0</v>
       </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="n">
@@ -30963,6 +34743,12 @@
       <c r="S517" t="n">
         <v>0</v>
       </c>
+      <c r="T517" t="n">
+        <v>100</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="1" t="n">
@@ -31022,6 +34808,12 @@
       <c r="S518" t="n">
         <v>0</v>
       </c>
+      <c r="T518" t="n">
+        <v>100</v>
+      </c>
+      <c r="U518" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="1" t="n">
@@ -31081,6 +34873,12 @@
       <c r="S519" t="n">
         <v>1</v>
       </c>
+      <c r="T519" t="n">
+        <v>100</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="1" t="n">
@@ -31140,6 +34938,12 @@
       <c r="S520" t="n">
         <v>0</v>
       </c>
+      <c r="T520" t="n">
+        <v>75</v>
+      </c>
+      <c r="U520" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="n">
@@ -31199,6 +35003,16 @@
       <c r="S521" t="n">
         <v>0</v>
       </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="1" t="n">
@@ -31258,6 +35072,12 @@
       <c r="S522" t="n">
         <v>0</v>
       </c>
+      <c r="T522" t="n">
+        <v>100</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="n">
@@ -31317,6 +35137,12 @@
       <c r="S523" t="n">
         <v>0</v>
       </c>
+      <c r="T523" t="n">
+        <v>0</v>
+      </c>
+      <c r="U523" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="n">
@@ -31376,6 +35202,12 @@
       <c r="S524" t="n">
         <v>0</v>
       </c>
+      <c r="T524" t="n">
+        <v>50</v>
+      </c>
+      <c r="U524" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="n">
@@ -31435,6 +35267,12 @@
       <c r="S525" t="n">
         <v>0</v>
       </c>
+      <c r="T525" t="n">
+        <v>100</v>
+      </c>
+      <c r="U525" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
@@ -31494,6 +35332,12 @@
       <c r="S526" t="n">
         <v>0</v>
       </c>
+      <c r="T526" t="n">
+        <v>100</v>
+      </c>
+      <c r="U526" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="n">
@@ -31553,6 +35397,12 @@
       <c r="S527" t="n">
         <v>0</v>
       </c>
+      <c r="T527" t="n">
+        <v>75</v>
+      </c>
+      <c r="U527" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="1" t="n">
@@ -31612,6 +35462,12 @@
       <c r="S528" t="n">
         <v>0</v>
       </c>
+      <c r="T528" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U528" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="n">
@@ -31671,6 +35527,12 @@
       <c r="S529" t="n">
         <v>0</v>
       </c>
+      <c r="T529" t="n">
+        <v>100</v>
+      </c>
+      <c r="U529" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="n">
@@ -31730,6 +35592,12 @@
       <c r="S530" t="n">
         <v>0</v>
       </c>
+      <c r="T530" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="U530" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="1" t="n">
@@ -31789,6 +35657,12 @@
       <c r="S531" t="n">
         <v>0</v>
       </c>
+      <c r="T531" t="n">
+        <v>100</v>
+      </c>
+      <c r="U531" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="n">
@@ -31848,6 +35722,12 @@
       <c r="S532" t="n">
         <v>0</v>
       </c>
+      <c r="T532" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U532" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="1" t="n">
@@ -31907,6 +35787,12 @@
       <c r="S533" t="n">
         <v>0</v>
       </c>
+      <c r="T533" t="n">
+        <v>100</v>
+      </c>
+      <c r="U533" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="n">
@@ -31966,6 +35852,12 @@
       <c r="S534" t="n">
         <v>0</v>
       </c>
+      <c r="T534" t="n">
+        <v>100</v>
+      </c>
+      <c r="U534" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="1" t="n">
@@ -32025,6 +35917,12 @@
       <c r="S535" t="n">
         <v>0</v>
       </c>
+      <c r="T535" t="n">
+        <v>100</v>
+      </c>
+      <c r="U535" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="1" t="n">
@@ -32084,6 +35982,12 @@
       <c r="S536" t="n">
         <v>0</v>
       </c>
+      <c r="T536" t="n">
+        <v>100</v>
+      </c>
+      <c r="U536" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="1" t="n">
@@ -32143,6 +36047,16 @@
       <c r="S537" t="n">
         <v>0</v>
       </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="1" t="n">
@@ -32202,6 +36116,16 @@
       <c r="S538" t="n">
         <v>0</v>
       </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="1" t="n">
@@ -32261,6 +36185,12 @@
       <c r="S539" t="n">
         <v>0</v>
       </c>
+      <c r="T539" t="n">
+        <v>50</v>
+      </c>
+      <c r="U539" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="1" t="n">
@@ -32320,6 +36250,12 @@
       <c r="S540" t="n">
         <v>0</v>
       </c>
+      <c r="T540" t="n">
+        <v>20</v>
+      </c>
+      <c r="U540" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="n">
@@ -32379,6 +36315,12 @@
       <c r="S541" t="n">
         <v>0</v>
       </c>
+      <c r="T541" t="n">
+        <v>16.6666666666666</v>
+      </c>
+      <c r="U541" t="n">
+        <v>83.3333333333333</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="n">
@@ -32438,6 +36380,12 @@
       <c r="S542" t="n">
         <v>0</v>
       </c>
+      <c r="T542" t="n">
+        <v>16.6666666666666</v>
+      </c>
+      <c r="U542" t="n">
+        <v>83.3333333333333</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="1" t="n">
@@ -32497,6 +36445,12 @@
       <c r="S543" t="n">
         <v>0</v>
       </c>
+      <c r="T543" t="n">
+        <v>100</v>
+      </c>
+      <c r="U543" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="1" t="n">
@@ -32556,6 +36510,12 @@
       <c r="S544" t="n">
         <v>0</v>
       </c>
+      <c r="T544" t="n">
+        <v>100</v>
+      </c>
+      <c r="U544" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="1" t="n">
@@ -32615,6 +36575,12 @@
       <c r="S545" t="n">
         <v>0</v>
       </c>
+      <c r="T545" t="n">
+        <v>100</v>
+      </c>
+      <c r="U545" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="1" t="n">
@@ -32674,6 +36640,16 @@
       <c r="S546" t="n">
         <v>0</v>
       </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="1" t="n">
@@ -32733,6 +36709,12 @@
       <c r="S547" t="n">
         <v>0</v>
       </c>
+      <c r="T547" t="n">
+        <v>100</v>
+      </c>
+      <c r="U547" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="n">
@@ -32792,6 +36774,16 @@
       <c r="S548" t="n">
         <v>0</v>
       </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="1" t="n">
@@ -32851,6 +36843,12 @@
       <c r="S549" t="n">
         <v>0</v>
       </c>
+      <c r="T549" t="n">
+        <v>60</v>
+      </c>
+      <c r="U549" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="1" t="n">
@@ -32910,6 +36908,12 @@
       <c r="S550" t="n">
         <v>0</v>
       </c>
+      <c r="T550" t="n">
+        <v>100</v>
+      </c>
+      <c r="U550" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="1" t="n">
@@ -32969,6 +36973,12 @@
       <c r="S551" t="n">
         <v>0</v>
       </c>
+      <c r="T551" t="n">
+        <v>100</v>
+      </c>
+      <c r="U551" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="n">
@@ -33028,6 +37038,12 @@
       <c r="S552" t="n">
         <v>0</v>
       </c>
+      <c r="T552" t="n">
+        <v>100</v>
+      </c>
+      <c r="U552" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="1" t="n">
@@ -33087,6 +37103,12 @@
       <c r="S553" t="n">
         <v>0</v>
       </c>
+      <c r="T553" t="n">
+        <v>100</v>
+      </c>
+      <c r="U553" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="n">
@@ -33146,6 +37168,12 @@
       <c r="S554" t="n">
         <v>0</v>
       </c>
+      <c r="T554" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U554" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="1" t="n">
@@ -33205,6 +37233,12 @@
       <c r="S555" t="n">
         <v>0</v>
       </c>
+      <c r="T555" t="n">
+        <v>100</v>
+      </c>
+      <c r="U555" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="1" t="n">
@@ -33264,6 +37298,12 @@
       <c r="S556" t="n">
         <v>0</v>
       </c>
+      <c r="T556" t="n">
+        <v>100</v>
+      </c>
+      <c r="U556" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="1" t="n">
@@ -33323,6 +37363,12 @@
       <c r="S557" t="n">
         <v>1</v>
       </c>
+      <c r="T557" t="n">
+        <v>100</v>
+      </c>
+      <c r="U557" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="1" t="n">
@@ -33382,6 +37428,12 @@
       <c r="S558" t="n">
         <v>0</v>
       </c>
+      <c r="T558" t="n">
+        <v>81.8181818181818</v>
+      </c>
+      <c r="U558" t="n">
+        <v>18.1818181818181</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="1" t="n">
@@ -33441,6 +37493,12 @@
       <c r="S559" t="n">
         <v>0</v>
       </c>
+      <c r="T559" t="n">
+        <v>100</v>
+      </c>
+      <c r="U559" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="n">
@@ -33500,6 +37558,16 @@
       <c r="S560" t="n">
         <v>0</v>
       </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="1" t="n">
@@ -33559,6 +37627,16 @@
       <c r="S561" t="n">
         <v>0</v>
       </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="1" t="n">
@@ -33618,6 +37696,16 @@
       <c r="S562" t="n">
         <v>0</v>
       </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="1" t="n">
@@ -33677,6 +37765,16 @@
       <c r="S563" t="n">
         <v>0</v>
       </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="1" t="n">
@@ -33736,6 +37834,12 @@
       <c r="S564" t="n">
         <v>0</v>
       </c>
+      <c r="T564" t="n">
+        <v>50</v>
+      </c>
+      <c r="U564" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="1" t="n">
@@ -33795,6 +37899,12 @@
       <c r="S565" t="n">
         <v>0</v>
       </c>
+      <c r="T565" t="n">
+        <v>100</v>
+      </c>
+      <c r="U565" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="n">
@@ -33854,6 +37964,12 @@
       <c r="S566" t="n">
         <v>0</v>
       </c>
+      <c r="T566" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U566" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="1" t="n">
@@ -33913,6 +38029,12 @@
       <c r="S567" t="n">
         <v>0</v>
       </c>
+      <c r="T567" t="n">
+        <v>100</v>
+      </c>
+      <c r="U567" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="1" t="n">
@@ -33972,6 +38094,12 @@
       <c r="S568" t="n">
         <v>0</v>
       </c>
+      <c r="T568" t="n">
+        <v>100</v>
+      </c>
+      <c r="U568" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="1" t="n">
@@ -34031,6 +38159,16 @@
       <c r="S569" t="n">
         <v>0</v>
       </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="1" t="n">
@@ -34090,6 +38228,12 @@
       <c r="S570" t="n">
         <v>0</v>
       </c>
+      <c r="T570" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U570" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
@@ -34149,6 +38293,12 @@
       <c r="S571" t="n">
         <v>0</v>
       </c>
+      <c r="T571" t="n">
+        <v>100</v>
+      </c>
+      <c r="U571" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
@@ -34208,6 +38358,12 @@
       <c r="S572" t="n">
         <v>0</v>
       </c>
+      <c r="T572" t="n">
+        <v>100</v>
+      </c>
+      <c r="U572" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
@@ -34267,6 +38423,12 @@
       <c r="S573" t="n">
         <v>0</v>
       </c>
+      <c r="T573" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U573" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="1" t="n">
@@ -34326,6 +38488,12 @@
       <c r="S574" t="n">
         <v>0</v>
       </c>
+      <c r="T574" t="n">
+        <v>100</v>
+      </c>
+      <c r="U574" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="1" t="n">
@@ -34385,6 +38553,12 @@
       <c r="S575" t="n">
         <v>0</v>
       </c>
+      <c r="T575" t="n">
+        <v>100</v>
+      </c>
+      <c r="U575" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="1" t="n">
@@ -34444,6 +38618,12 @@
       <c r="S576" t="n">
         <v>0</v>
       </c>
+      <c r="T576" t="n">
+        <v>100</v>
+      </c>
+      <c r="U576" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="1" t="n">
@@ -34503,6 +38683,12 @@
       <c r="S577" t="n">
         <v>0</v>
       </c>
+      <c r="T577" t="n">
+        <v>100</v>
+      </c>
+      <c r="U577" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="1" t="n">
@@ -34562,6 +38748,16 @@
       <c r="S578" t="n">
         <v>0</v>
       </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="1" t="n">
@@ -34621,6 +38817,16 @@
       <c r="S579" t="n">
         <v>0</v>
       </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="1" t="n">
@@ -34680,6 +38886,12 @@
       <c r="S580" t="n">
         <v>1</v>
       </c>
+      <c r="T580" t="n">
+        <v>50</v>
+      </c>
+      <c r="U580" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="1" t="n">
@@ -34739,6 +38951,12 @@
       <c r="S581" t="n">
         <v>0</v>
       </c>
+      <c r="T581" t="n">
+        <v>50</v>
+      </c>
+      <c r="U581" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="1" t="n">
@@ -34798,6 +39016,12 @@
       <c r="S582" t="n">
         <v>0</v>
       </c>
+      <c r="T582" t="n">
+        <v>0</v>
+      </c>
+      <c r="U582" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="1" t="n">
@@ -34857,6 +39081,12 @@
       <c r="S583" t="n">
         <v>0</v>
       </c>
+      <c r="T583" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U583" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="1" t="n">
@@ -34916,6 +39146,12 @@
       <c r="S584" t="n">
         <v>2</v>
       </c>
+      <c r="T584" t="n">
+        <v>100</v>
+      </c>
+      <c r="U584" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="1" t="n">
@@ -34975,6 +39211,12 @@
       <c r="S585" t="n">
         <v>0</v>
       </c>
+      <c r="T585" t="n">
+        <v>100</v>
+      </c>
+      <c r="U585" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="1" t="n">
@@ -35034,6 +39276,16 @@
       <c r="S586" t="n">
         <v>0</v>
       </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="1" t="n">
@@ -35093,6 +39345,16 @@
       <c r="S587" t="n">
         <v>0</v>
       </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="1" t="n">
@@ -35152,6 +39414,16 @@
       <c r="S588" t="n">
         <v>0</v>
       </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="1" t="n">
@@ -35211,6 +39483,16 @@
       <c r="S589" t="n">
         <v>0</v>
       </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="1" t="n">
@@ -35270,6 +39552,16 @@
       <c r="S590" t="n">
         <v>0</v>
       </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="1" t="n">
@@ -35329,6 +39621,16 @@
       <c r="S591" t="n">
         <v>0</v>
       </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="1" t="n">
@@ -35388,6 +39690,12 @@
       <c r="S592" t="n">
         <v>0</v>
       </c>
+      <c r="T592" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U592" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="1" t="n">
@@ -35447,6 +39755,12 @@
       <c r="S593" t="n">
         <v>0</v>
       </c>
+      <c r="T593" t="n">
+        <v>75</v>
+      </c>
+      <c r="U593" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1" t="n">
@@ -35506,6 +39820,12 @@
       <c r="S594" t="n">
         <v>0</v>
       </c>
+      <c r="T594" t="n">
+        <v>100</v>
+      </c>
+      <c r="U594" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="1" t="n">
@@ -35565,6 +39885,16 @@
       <c r="S595" t="n">
         <v>0</v>
       </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="1" t="n">
@@ -35624,6 +39954,16 @@
       <c r="S596" t="n">
         <v>0</v>
       </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="1" t="n">
@@ -35683,6 +40023,12 @@
       <c r="S597" t="n">
         <v>0</v>
       </c>
+      <c r="T597" t="n">
+        <v>100</v>
+      </c>
+      <c r="U597" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="1" t="n">
@@ -35742,6 +40088,12 @@
       <c r="S598" t="n">
         <v>0</v>
       </c>
+      <c r="T598" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U598" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="1" t="n">
@@ -35801,6 +40153,12 @@
       <c r="S599" t="n">
         <v>0</v>
       </c>
+      <c r="T599" t="n">
+        <v>100</v>
+      </c>
+      <c r="U599" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="n">
@@ -35860,6 +40218,12 @@
       <c r="S600" t="n">
         <v>1</v>
       </c>
+      <c r="T600" t="n">
+        <v>100</v>
+      </c>
+      <c r="U600" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
@@ -35919,6 +40283,12 @@
       <c r="S601" t="n">
         <v>0</v>
       </c>
+      <c r="T601" t="n">
+        <v>100</v>
+      </c>
+      <c r="U601" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
@@ -35978,6 +40348,12 @@
       <c r="S602" t="n">
         <v>0</v>
       </c>
+      <c r="T602" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U602" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
@@ -36037,6 +40413,16 @@
       <c r="S603" t="n">
         <v>0</v>
       </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="1" t="n">
@@ -36096,6 +40482,12 @@
       <c r="S604" t="n">
         <v>0</v>
       </c>
+      <c r="T604" t="n">
+        <v>100</v>
+      </c>
+      <c r="U604" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="1" t="n">
@@ -36155,6 +40547,12 @@
       <c r="S605" t="n">
         <v>0</v>
       </c>
+      <c r="T605" t="n">
+        <v>100</v>
+      </c>
+      <c r="U605" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="1" t="n">
@@ -36214,6 +40612,12 @@
       <c r="S606" t="n">
         <v>0</v>
       </c>
+      <c r="T606" t="n">
+        <v>100</v>
+      </c>
+      <c r="U606" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="1" t="n">
@@ -36273,6 +40677,16 @@
       <c r="S607" t="n">
         <v>0</v>
       </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="1" t="n">
@@ -36332,6 +40746,12 @@
       <c r="S608" t="n">
         <v>0</v>
       </c>
+      <c r="T608" t="n">
+        <v>100</v>
+      </c>
+      <c r="U608" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="1" t="n">
@@ -36391,6 +40811,12 @@
       <c r="S609" t="n">
         <v>0</v>
       </c>
+      <c r="T609" t="n">
+        <v>100</v>
+      </c>
+      <c r="U609" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="1" t="n">
@@ -36450,6 +40876,16 @@
       <c r="S610" t="n">
         <v>0</v>
       </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="1" t="n">
@@ -36509,6 +40945,16 @@
       <c r="S611" t="n">
         <v>0</v>
       </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="1" t="n">
@@ -36568,6 +41014,16 @@
       <c r="S612" t="n">
         <v>0</v>
       </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="1" t="n">
@@ -36627,6 +41083,16 @@
       <c r="S613" t="n">
         <v>0</v>
       </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="1" t="n">
@@ -36686,6 +41152,16 @@
       <c r="S614" t="n">
         <v>0</v>
       </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="1" t="n">
@@ -36745,6 +41221,12 @@
       <c r="S615" t="n">
         <v>1</v>
       </c>
+      <c r="T615" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U615" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="1" t="n">
@@ -36804,6 +41286,16 @@
       <c r="S616" t="n">
         <v>0</v>
       </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="1" t="n">
@@ -36863,6 +41355,16 @@
       <c r="S617" t="n">
         <v>0</v>
       </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="1" t="n">
@@ -36922,6 +41424,12 @@
       <c r="S618" t="n">
         <v>0</v>
       </c>
+      <c r="T618" t="n">
+        <v>100</v>
+      </c>
+      <c r="U618" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="1" t="n">
@@ -36981,6 +41489,12 @@
       <c r="S619" t="n">
         <v>0</v>
       </c>
+      <c r="T619" t="n">
+        <v>100</v>
+      </c>
+      <c r="U619" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="1" t="n">
@@ -37040,6 +41554,12 @@
       <c r="S620" t="n">
         <v>0</v>
       </c>
+      <c r="T620" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U620" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="1" t="n">
@@ -37099,6 +41619,12 @@
       <c r="S621" t="n">
         <v>0</v>
       </c>
+      <c r="T621" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="U621" t="n">
+        <v>66.6666666666666</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="1" t="n">
@@ -37158,6 +41684,12 @@
       <c r="S622" t="n">
         <v>0</v>
       </c>
+      <c r="T622" t="n">
+        <v>100</v>
+      </c>
+      <c r="U622" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="1" t="n">
@@ -37217,6 +41749,12 @@
       <c r="S623" t="n">
         <v>0</v>
       </c>
+      <c r="T623" t="n">
+        <v>100</v>
+      </c>
+      <c r="U623" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="1" t="n">
@@ -37276,6 +41814,12 @@
       <c r="S624" t="n">
         <v>0</v>
       </c>
+      <c r="T624" t="n">
+        <v>60</v>
+      </c>
+      <c r="U624" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="1" t="n">
@@ -37335,6 +41879,16 @@
       <c r="S625" t="n">
         <v>0</v>
       </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="1" t="n">
@@ -37394,6 +41948,16 @@
       <c r="S626" t="n">
         <v>0</v>
       </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="1" t="n">
@@ -37453,6 +42017,16 @@
       <c r="S627" t="n">
         <v>0</v>
       </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="1" t="n">
@@ -37512,6 +42086,16 @@
       <c r="S628" t="n">
         <v>0</v>
       </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="1" t="n">
@@ -37571,6 +42155,16 @@
       <c r="S629" t="n">
         <v>0</v>
       </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="1" t="n">
@@ -37630,6 +42224,16 @@
       <c r="S630" t="n">
         <v>0</v>
       </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="1" t="n">
@@ -37689,6 +42293,16 @@
       <c r="S631" t="n">
         <v>0</v>
       </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="1" t="n">
@@ -37748,6 +42362,16 @@
       <c r="S632" t="n">
         <v>0</v>
       </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="1" t="n">
@@ -37807,6 +42431,16 @@
       <c r="S633" t="n">
         <v>0</v>
       </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="1" t="n">
@@ -37866,6 +42500,12 @@
       <c r="S634" t="n">
         <v>0</v>
       </c>
+      <c r="T634" t="n">
+        <v>50</v>
+      </c>
+      <c r="U634" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="1" t="n">
@@ -37925,6 +42565,12 @@
       <c r="S635" t="n">
         <v>0</v>
       </c>
+      <c r="T635" t="n">
+        <v>0</v>
+      </c>
+      <c r="U635" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="1" t="n">
@@ -37984,6 +42630,12 @@
       <c r="S636" t="n">
         <v>0</v>
       </c>
+      <c r="T636" t="n">
+        <v>100</v>
+      </c>
+      <c r="U636" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="1" t="n">
@@ -38043,6 +42695,12 @@
       <c r="S637" t="n">
         <v>0</v>
       </c>
+      <c r="T637" t="n">
+        <v>100</v>
+      </c>
+      <c r="U637" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="1" t="n">
@@ -38102,6 +42760,12 @@
       <c r="S638" t="n">
         <v>0</v>
       </c>
+      <c r="T638" t="n">
+        <v>100</v>
+      </c>
+      <c r="U638" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="1" t="n">
@@ -38161,6 +42825,16 @@
       <c r="S639" t="n">
         <v>0</v>
       </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="1" t="n">
@@ -38220,6 +42894,12 @@
       <c r="S640" t="n">
         <v>0</v>
       </c>
+      <c r="T640" t="n">
+        <v>100</v>
+      </c>
+      <c r="U640" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="1" t="n">
@@ -38279,6 +42959,12 @@
       <c r="S641" t="n">
         <v>0</v>
       </c>
+      <c r="T641" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U641" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="1" t="n">
@@ -38338,6 +43024,12 @@
       <c r="S642" t="n">
         <v>0</v>
       </c>
+      <c r="T642" t="n">
+        <v>100</v>
+      </c>
+      <c r="U642" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="1" t="n">
@@ -38397,6 +43089,12 @@
       <c r="S643" t="n">
         <v>0</v>
       </c>
+      <c r="T643" t="n">
+        <v>100</v>
+      </c>
+      <c r="U643" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="1" t="n">
@@ -38456,6 +43154,12 @@
       <c r="S644" t="n">
         <v>0</v>
       </c>
+      <c r="T644" t="n">
+        <v>75</v>
+      </c>
+      <c r="U644" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="1" t="n">
@@ -38515,6 +43219,12 @@
       <c r="S645" t="n">
         <v>0</v>
       </c>
+      <c r="T645" t="n">
+        <v>100</v>
+      </c>
+      <c r="U645" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="1" t="n">
@@ -38574,6 +43284,12 @@
       <c r="S646" t="n">
         <v>0</v>
       </c>
+      <c r="T646" t="n">
+        <v>0</v>
+      </c>
+      <c r="U646" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="1" t="n">
@@ -38633,6 +43349,12 @@
       <c r="S647" t="n">
         <v>0</v>
       </c>
+      <c r="T647" t="n">
+        <v>50</v>
+      </c>
+      <c r="U647" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="1" t="n">
@@ -38692,6 +43414,12 @@
       <c r="S648" t="n">
         <v>0</v>
       </c>
+      <c r="T648" t="n">
+        <v>50</v>
+      </c>
+      <c r="U648" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="1" t="n">
@@ -38751,6 +43479,12 @@
       <c r="S649" t="n">
         <v>2</v>
       </c>
+      <c r="T649" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U649" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="1" t="n">
@@ -38810,6 +43544,16 @@
       <c r="S650" t="n">
         <v>0</v>
       </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="1" t="n">
@@ -38869,6 +43613,16 @@
       <c r="S651" t="n">
         <v>0</v>
       </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="1" t="n">
@@ -38928,6 +43682,16 @@
       <c r="S652" t="n">
         <v>0</v>
       </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
@@ -38987,6 +43751,16 @@
       <c r="S653" t="n">
         <v>0</v>
       </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="1" t="n">
@@ -39046,6 +43820,12 @@
       <c r="S654" t="n">
         <v>0</v>
       </c>
+      <c r="T654" t="n">
+        <v>100</v>
+      </c>
+      <c r="U654" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="1" t="n">
@@ -39105,6 +43885,12 @@
       <c r="S655" t="n">
         <v>0</v>
       </c>
+      <c r="T655" t="n">
+        <v>100</v>
+      </c>
+      <c r="U655" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="1" t="n">
@@ -39164,6 +43950,12 @@
       <c r="S656" t="n">
         <v>0</v>
       </c>
+      <c r="T656" t="n">
+        <v>50</v>
+      </c>
+      <c r="U656" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="1" t="n">
@@ -39223,6 +44015,12 @@
       <c r="S657" t="n">
         <v>0</v>
       </c>
+      <c r="T657" t="n">
+        <v>100</v>
+      </c>
+      <c r="U657" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="1" t="n">
@@ -39282,6 +44080,12 @@
       <c r="S658" t="n">
         <v>0</v>
       </c>
+      <c r="T658" t="n">
+        <v>100</v>
+      </c>
+      <c r="U658" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="1" t="n">
@@ -39341,6 +44145,12 @@
       <c r="S659" t="n">
         <v>0</v>
       </c>
+      <c r="T659" t="n">
+        <v>100</v>
+      </c>
+      <c r="U659" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="1" t="n">
@@ -39400,6 +44210,16 @@
       <c r="S660" t="n">
         <v>0</v>
       </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="1" t="n">
@@ -39459,6 +44279,12 @@
       <c r="S661" t="n">
         <v>0</v>
       </c>
+      <c r="T661" t="n">
+        <v>100</v>
+      </c>
+      <c r="U661" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="1" t="n">
@@ -39518,6 +44344,16 @@
       <c r="S662" t="n">
         <v>0</v>
       </c>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="1" t="n">
@@ -39577,6 +44413,12 @@
       <c r="S663" t="n">
         <v>0</v>
       </c>
+      <c r="T663" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U663" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="1" t="n">
@@ -39636,6 +44478,16 @@
       <c r="S664" t="n">
         <v>0</v>
       </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="1" t="n">
@@ -39695,6 +44547,16 @@
       <c r="S665" t="n">
         <v>0</v>
       </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="1" t="n">
@@ -39754,6 +44616,12 @@
       <c r="S666" t="n">
         <v>0</v>
       </c>
+      <c r="T666" t="n">
+        <v>50</v>
+      </c>
+      <c r="U666" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
@@ -39813,6 +44681,12 @@
       <c r="S667" t="n">
         <v>0</v>
       </c>
+      <c r="T667" t="n">
+        <v>50</v>
+      </c>
+      <c r="U667" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="1" t="n">
@@ -39872,6 +44746,12 @@
       <c r="S668" t="n">
         <v>0</v>
       </c>
+      <c r="T668" t="n">
+        <v>75</v>
+      </c>
+      <c r="U668" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
@@ -39931,6 +44811,16 @@
       <c r="S669" t="n">
         <v>0</v>
       </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
@@ -39990,6 +44880,12 @@
       <c r="S670" t="n">
         <v>0</v>
       </c>
+      <c r="T670" t="n">
+        <v>75</v>
+      </c>
+      <c r="U670" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
@@ -40049,6 +44945,12 @@
       <c r="S671" t="n">
         <v>0</v>
       </c>
+      <c r="T671" t="n">
+        <v>100</v>
+      </c>
+      <c r="U671" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
@@ -40108,6 +45010,12 @@
       <c r="S672" t="n">
         <v>0</v>
       </c>
+      <c r="T672" t="n">
+        <v>100</v>
+      </c>
+      <c r="U672" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="1" t="n">
@@ -40167,6 +45075,12 @@
       <c r="S673" t="n">
         <v>0</v>
       </c>
+      <c r="T673" t="n">
+        <v>75</v>
+      </c>
+      <c r="U673" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="1" t="n">
@@ -40226,6 +45140,12 @@
       <c r="S674" t="n">
         <v>0</v>
       </c>
+      <c r="T674" t="n">
+        <v>80</v>
+      </c>
+      <c r="U674" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="1" t="n">
@@ -40284,6 +45204,12 @@
       </c>
       <c r="S675" t="n">
         <v>0</v>
+      </c>
+      <c r="T675" t="n">
+        <v>75</v>
+      </c>
+      <c r="U675" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
